--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -346,10 +346,10 @@
     <t xml:space="preserve">Score</t>
   </si>
   <si>
-    <t xml:space="preserve">0 hard/0 soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10000 hard/0 soft</t>
+    <t xml:space="preserve">0hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10000hard/0soft</t>
   </si>
 </sst>
 </file>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -13,11 +13,26 @@
     <sheet name="Rooms" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Speakers" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Talks" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="talkTypeOfTimeSlotSetup" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="testTimeSlotWithMatchingTalkType" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="talkHasUnavailableRoomSetup" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="talkWithAvailableRoom" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="talkWithRoomWithUnavailableTimeslot" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="talkTypeOfTimeslot_setup" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="talkTypeOfTimeslot_timeslotWithMatchingTalkType" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="talkTypeOfTimeslot_timeslotWithNonMatchingTalkType" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="talkHasUnavailableRoom_setup" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom_2" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom_2" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="roomConflict_setup" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="roomConflict_talksInSameRoomWithOverlappingTimeslots" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="roomConflict_talksInDifferentRoomsWithOverlappingTimeslots" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="talkWithUnavailableSpeaker_setup" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker_2" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers_2" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="23" state="visible" r:id="rId24"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="24" state="visible" r:id="rId25"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_3" sheetId="25" state="visible" r:id="rId26"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="133">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -214,55 +229,79 @@
     <t xml:space="preserve">Tags</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 2018-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkType1</t>
+    <t xml:space="preserve">Mon 2018-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkTypeOfTimeslot_talkType1</t>
   </si>
   <si>
     <t xml:space="preserve">11:00</t>
   </si>
   <si>
-    <t xml:space="preserve">11:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkType2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:00</t>
+    <t xml:space="preserve">Tue 2018-01-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_talkType1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wed 2018-01-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roomConflict_talkType1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 2018-01-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_talkType1</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">10:15-12:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:15-11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:30-12:15</t>
+    <t xml:space="preserve">09:00-10:00</t>
   </si>
   <si>
     <t xml:space="preserve">10:00-11:00</t>
   </si>
   <si>
-    <t xml:space="preserve">10:00-11:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large, Recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R 2</t>
+    <t xml:space="preserve">09:30-10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkTypeOfTimeslot_room1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_room1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_room2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_room3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_room4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roomConflict_room1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roomConflict_room2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_room1</t>
   </si>
   <si>
     <t xml:space="preserve">Required timeslot tags</t>
@@ -289,6 +328,18 @@
     <t xml:space="preserve">Undesired room tags</t>
   </si>
   <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Code</t>
   </si>
   <si>
@@ -328,10 +379,94 @@
     <t xml:space="preserve">Room</t>
   </si>
   <si>
-    <t xml:space="preserve">talk1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talk2</t>
+    <t xml:space="preserve">talkTypeOfTimeslot_talk1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkTypeOfTimeslot_talk2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_talk1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkHasUnavailableRoom_talk2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roomConflict_talk1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roomConflict_talk2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_talk1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_talk2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker1, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_talk3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_talk4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker2, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeaker_talk5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker3, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker4</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Constraint package</t>
@@ -350,6 +485,12 @@
   </si>
   <si>
     <t xml:space="preserve">-10000hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1hard/0soft</t>
   </si>
 </sst>
 </file>
@@ -360,7 +501,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -388,6 +529,11 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -455,7 +601,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -465,6 +611,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -480,15 +630,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -500,7 +654,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -945,6 +1103,1581 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F9:H9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F9:H9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F9:H9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F9:H9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -956,16 +2689,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>102</v>
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="4"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -974,16 +2707,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>36</v>
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -992,16 +2725,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>106</v>
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="5"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1010,13 +2743,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1025,58 +2758,58 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>61</v>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
+        <v>85</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1088,6 +2821,173 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1103,12 +3003,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="6.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="8.67"/>
   </cols>
@@ -1130,7 +3030,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
@@ -1145,12 +3045,12 @@
       </c>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>65</v>
@@ -1161,70 +3061,1117 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>64</v>
+      <c r="D6" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1240,38 +4187,44 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="16" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="4" style="0" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="15" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
+      <c r="K1" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>59</v>
@@ -1280,85 +4233,248 @@
         <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:H1"/>
+  <mergeCells count="4">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1375,7 +4491,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U50"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
@@ -1405,1153 +4521,262 @@
         <v>61</v>
       </c>
       <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="L1" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="N1" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
-      <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="2"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="2"/>
-      <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="2"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
-      <c r="U49" s="5"/>
-    </row>
+    <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J1:O1"/>
+  <mergeCells count="4">
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2598,64 +4823,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -2664,12 +4889,12 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
@@ -2692,19 +4917,19 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="6"/>
+      <c r="S2" s="9"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2723,7 +4948,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="6"/>
+      <c r="S3" s="9"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
@@ -2748,21 +4973,27 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="6"/>
+      <c r="S4" s="9"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -2773,21 +5004,27 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="6"/>
+      <c r="S5" s="9"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2798,7 +5035,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="6"/>
+      <c r="S6" s="9"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -2823,21 +5060,27 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="6"/>
+      <c r="S7" s="9"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2848,21 +5091,27 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
-      <c r="S8" s="6"/>
+      <c r="S8" s="9"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2873,7 +5122,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="6"/>
+      <c r="S9" s="9"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
@@ -2898,21 +5147,29 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="9"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+    <row r="11" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2923,21 +5180,29 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
-      <c r="S11" s="6"/>
+      <c r="S11" s="9"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
+    <row r="12" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2948,21 +5213,29 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="6"/>
+      <c r="S12" s="9"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+    <row r="13" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2973,21 +5246,29 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="6"/>
+      <c r="S13" s="9"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+    <row r="14" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2998,21 +5279,29 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="6"/>
+      <c r="S14" s="9"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
+    <row r="15" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -3023,7 +5312,7 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="6"/>
+      <c r="S15" s="9"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
@@ -3048,7 +5337,7 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="6"/>
+      <c r="S16" s="9"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
@@ -3073,7 +5362,7 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="6"/>
+      <c r="S17" s="9"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -3098,7 +5387,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="6"/>
+      <c r="S18" s="9"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
@@ -3123,7 +5412,7 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="6"/>
+      <c r="S19" s="9"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
@@ -3148,7 +5437,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="6"/>
+      <c r="S20" s="9"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -3173,7 +5462,7 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="6"/>
+      <c r="S21" s="9"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
@@ -3198,7 +5487,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="6"/>
+      <c r="S22" s="9"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
@@ -3223,7 +5512,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="6"/>
+      <c r="S23" s="9"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -3248,7 +5537,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
-      <c r="S24" s="6"/>
+      <c r="S24" s="9"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
@@ -3273,7 +5562,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="6"/>
+      <c r="S25" s="9"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
@@ -3298,7 +5587,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="6"/>
+      <c r="S26" s="9"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
@@ -3323,7 +5612,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="6"/>
+      <c r="S27" s="9"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
@@ -3348,7 +5637,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="6"/>
+      <c r="S28" s="9"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
@@ -3373,7 +5662,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="6"/>
+      <c r="S29" s="9"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
@@ -3398,7 +5687,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="6"/>
+      <c r="S30" s="9"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
@@ -3423,7 +5712,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="6"/>
+      <c r="S31" s="9"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -3448,7 +5737,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
-      <c r="S32" s="6"/>
+      <c r="S32" s="9"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
@@ -3473,7 +5762,7 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="6"/>
+      <c r="S33" s="9"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
@@ -3498,7 +5787,7 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="6"/>
+      <c r="S34" s="9"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
@@ -3523,7 +5812,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="6"/>
+      <c r="S35" s="9"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
@@ -3548,7 +5837,7 @@
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
-      <c r="S36" s="6"/>
+      <c r="S36" s="9"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
@@ -3573,7 +5862,7 @@
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
-      <c r="S37" s="6"/>
+      <c r="S37" s="9"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
@@ -3598,7 +5887,7 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
-      <c r="S38" s="6"/>
+      <c r="S38" s="9"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -3623,7 +5912,7 @@
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="6"/>
+      <c r="S39" s="9"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
@@ -3648,7 +5937,7 @@
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
-      <c r="S40" s="6"/>
+      <c r="S40" s="9"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
@@ -3673,7 +5962,7 @@
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
-      <c r="S41" s="6"/>
+      <c r="S41" s="9"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -3698,7 +5987,7 @@
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="6"/>
+      <c r="S42" s="9"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
@@ -3723,7 +6012,7 @@
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
-      <c r="S43" s="6"/>
+      <c r="S43" s="9"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
@@ -3748,7 +6037,7 @@
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
-      <c r="S44" s="6"/>
+      <c r="S44" s="9"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
@@ -3773,7 +6062,7 @@
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
-      <c r="S45" s="6"/>
+      <c r="S45" s="9"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -3798,7 +6087,7 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="6"/>
+      <c r="S46" s="9"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
@@ -3823,7 +6112,7 @@
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
-      <c r="S47" s="6"/>
+      <c r="S47" s="9"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
@@ -3848,7 +6137,7 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
-      <c r="S48" s="6"/>
+      <c r="S48" s="9"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
@@ -3873,7 +6162,7 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="6"/>
+      <c r="S49" s="9"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
@@ -3898,7 +6187,7 @@
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
-      <c r="S50" s="6"/>
+      <c r="S50" s="9"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
@@ -3923,7 +6212,7 @@
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
-      <c r="S51" s="6"/>
+      <c r="S51" s="9"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
@@ -3948,7 +6237,7 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
-      <c r="S52" s="6"/>
+      <c r="S52" s="9"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
@@ -3973,7 +6262,7 @@
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
-      <c r="S53" s="6"/>
+      <c r="S53" s="9"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
@@ -3998,7 +6287,7 @@
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
-      <c r="S54" s="6"/>
+      <c r="S54" s="9"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
@@ -4023,7 +6312,7 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
-      <c r="S55" s="6"/>
+      <c r="S55" s="9"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
@@ -4048,7 +6337,7 @@
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
-      <c r="S56" s="6"/>
+      <c r="S56" s="9"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
@@ -4073,7 +6362,7 @@
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
-      <c r="S57" s="6"/>
+      <c r="S57" s="9"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
@@ -4098,7 +6387,7 @@
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
-      <c r="S58" s="6"/>
+      <c r="S58" s="9"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
@@ -4123,7 +6412,7 @@
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
-      <c r="S59" s="6"/>
+      <c r="S59" s="9"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
@@ -4148,7 +6437,7 @@
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="6"/>
+      <c r="S60" s="9"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
@@ -4173,7 +6462,7 @@
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
-      <c r="S61" s="6"/>
+      <c r="S61" s="9"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
@@ -4198,7 +6487,7 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
-      <c r="S62" s="6"/>
+      <c r="S62" s="9"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
@@ -4223,7 +6512,7 @@
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="6"/>
+      <c r="S63" s="9"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
@@ -4248,7 +6537,7 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="6"/>
+      <c r="S64" s="9"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
@@ -4273,7 +6562,7 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="6"/>
+      <c r="S65" s="9"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
@@ -4298,7 +6587,7 @@
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
-      <c r="S66" s="6"/>
+      <c r="S66" s="9"/>
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
@@ -4323,7 +6612,7 @@
       <c r="P67" s="2"/>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
-      <c r="S67" s="6"/>
+      <c r="S67" s="9"/>
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
@@ -4348,7 +6637,7 @@
       <c r="P68" s="2"/>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
-      <c r="S68" s="6"/>
+      <c r="S68" s="9"/>
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
@@ -4373,7 +6662,7 @@
       <c r="P69" s="2"/>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
-      <c r="S69" s="6"/>
+      <c r="S69" s="9"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
@@ -4398,7 +6687,7 @@
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
-      <c r="S70" s="6"/>
+      <c r="S70" s="9"/>
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
@@ -4423,7 +6712,7 @@
       <c r="P71" s="2"/>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
-      <c r="S71" s="6"/>
+      <c r="S71" s="9"/>
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
@@ -4448,16 +6737,88 @@
       <c r="P72" s="2"/>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
-      <c r="S72" s="7"/>
+      <c r="S72" s="9"/>
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="2"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="2"/>
+      <c r="W73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="9"/>
+      <c r="T74" s="2"/>
+      <c r="U74" s="2"/>
+      <c r="V74" s="2"/>
+      <c r="W74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="2"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="2"/>
+      <c r="W75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4483,7 +6844,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -4494,16 +6855,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>102</v>
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="4"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4512,16 +6873,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4530,16 +6891,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>105</v>
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="5"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4548,13 +6909,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4563,41 +6924,59 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4608,6 +6987,9 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4635,16 +7017,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>102</v>
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="4"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4653,16 +7035,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4671,16 +7053,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>105</v>
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="5"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4689,13 +7071,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4704,58 +7086,60 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
+      <c r="A7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4767,6 +7151,9 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4794,16 +7181,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>102</v>
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="4"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4812,16 +7199,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>36</v>
+        <v>127</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4830,16 +7217,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>105</v>
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="5"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4848,13 +7235,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4863,56 +7250,62 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
+      <c r="A7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4924,6 +7317,9 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4940,7 +7336,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -4951,16 +7347,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>102</v>
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="4"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4969,16 +7365,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4987,16 +7383,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>105</v>
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="5"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5005,13 +7401,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -5020,62 +7416,110 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>61</v>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5083,6 +7527,10 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F9:H9"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -33,6 +33,9 @@
     <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="23" state="visible" r:id="rId24"/>
     <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="24" state="visible" r:id="rId25"/>
     <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_3" sheetId="25" state="visible" r:id="rId26"/>
+    <sheet name="speakerConflict_setup" sheetId="26" state="visible" r:id="rId27"/>
+    <sheet name="speakerConflict_speakerHasNoConflictingTimeslots" sheetId="27" state="visible" r:id="rId28"/>
+    <sheet name="speakerConflict_speakerHasConflictingTimeslots" sheetId="28" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="140">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -268,6 +271,28 @@
     <t xml:space="preserve">talkWithUnavailableSpeaker_talkType1</t>
   </si>
   <si>
+    <t xml:space="preserve">Fri 2018-01-05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">speakerConflict</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_talkType1</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
@@ -304,6 +329,25 @@
     <t xml:space="preserve">talkWithUnavailableSpeaker_room1</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">speakerConflict</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_room1</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Required timeslot tags</t>
   </si>
   <si>
@@ -338,6 +382,25 @@
   </si>
   <si>
     <t xml:space="preserve">talkWithUnavailableSpeaker_speaker4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">speakerConflict</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_speaker1</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -469,6 +532,44 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">speakerConflict</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_talk1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">speakerConflict</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_talk2</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Constraint package</t>
   </si>
   <si>
@@ -491,6 +592,9 @@
   </si>
   <si>
     <t xml:space="preserve">-1hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">speakerConflict_talk1</t>
   </si>
 </sst>
 </file>
@@ -622,10 +726,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -647,6 +747,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1114,16 +1218,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1132,7 +1236,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -1141,7 +1245,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1150,16 +1254,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1168,13 +1272,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1187,26 +1291,26 @@
         <v>66</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -1221,60 +1325,60 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1283,11 +1387,11 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1327,16 +1431,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1345,7 +1449,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -1354,7 +1458,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1363,16 +1467,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1381,13 +1485,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1400,26 +1504,26 @@
         <v>66</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -1434,58 +1538,58 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="5"/>
+        <v>117</v>
+      </c>
+      <c r="C9" s="11"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1494,11 +1598,11 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1538,16 +1642,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1556,7 +1660,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -1565,7 +1669,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1574,16 +1678,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1592,13 +1696,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1611,26 +1715,26 @@
         <v>66</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -1645,59 +1749,59 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1706,11 +1810,11 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1750,16 +1854,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1768,7 +1872,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -1777,7 +1881,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1786,16 +1890,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1804,13 +1908,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1823,26 +1927,26 @@
         <v>66</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -1857,58 +1961,58 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="C9" s="11"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1916,11 +2020,11 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1960,16 +2064,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1978,7 +2082,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -1987,7 +2091,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1996,16 +2100,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2014,13 +2118,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2034,28 +2138,28 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -2069,37 +2173,37 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>85</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2140,16 +2244,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2158,7 +2262,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -2167,7 +2271,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2176,16 +2280,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2194,13 +2298,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2214,28 +2318,28 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -2249,41 +2353,41 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>85</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2324,16 +2428,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2342,7 +2446,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -2351,7 +2455,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2360,16 +2464,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2378,13 +2482,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2398,28 +2502,28 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -2433,40 +2537,40 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>85</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2507,16 +2611,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2525,7 +2629,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -2534,7 +2638,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2543,16 +2647,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2561,13 +2665,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2581,28 +2685,28 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -2616,39 +2720,39 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="7"/>
+        <v>86</v>
+      </c>
+      <c r="B8" s="6"/>
       <c r="C8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>120</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2689,16 +2793,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2707,16 +2811,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2725,16 +2829,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2743,13 +2847,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2762,26 +2866,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -2796,20 +2900,20 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2851,16 +2955,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2869,16 +2973,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2887,16 +2991,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2905,13 +3009,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2924,26 +3028,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -2958,22 +3062,22 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3186,11 +3290,60 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3220,16 +3373,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3238,16 +3391,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3256,16 +3409,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3274,13 +3427,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3293,26 +3446,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3327,21 +3480,21 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3383,16 +3536,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3401,16 +3554,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3419,16 +3572,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3437,13 +3590,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3456,26 +3609,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3490,21 +3643,21 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>122</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3546,16 +3699,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3564,16 +3717,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3582,16 +3735,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3600,13 +3753,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3619,26 +3772,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3653,22 +3806,22 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>122</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3710,16 +3863,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3728,16 +3881,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3746,16 +3899,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3764,13 +3917,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3783,26 +3936,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3817,21 +3970,21 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3873,16 +4026,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3891,16 +4044,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3909,16 +4062,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3927,13 +4080,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3946,26 +4099,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3980,21 +4133,21 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>125</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4036,16 +4189,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4054,16 +4207,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4072,16 +4225,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4090,13 +4243,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4109,26 +4262,26 @@
         <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -4143,21 +4296,21 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>127</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4182,19 +4335,519 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="4" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="15" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="16" style="0" width="8.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -4219,12 +4872,15 @@
         <v>72</v>
       </c>
       <c r="L1" s="4"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="M1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>59</v>
@@ -4233,38 +4889,45 @@
         <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>64</v>
@@ -4272,13 +4935,13 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
@@ -4286,94 +4949,94 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
@@ -4388,48 +5051,48 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
@@ -4451,30 +5114,67 @@
     </row>
     <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4491,7 +5191,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
@@ -4534,169 +5234,223 @@
         <v>72</v>
       </c>
       <c r="R1" s="4"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
+      <c r="S1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
+        <v>97</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
+        <v>98</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
+        <v>99</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>100</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+    </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4772,11 +5526,12 @@
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:U1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4823,64 +5578,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -4889,12 +5644,12 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
@@ -4917,7 +5672,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="9"/>
+      <c r="S2" s="8"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
@@ -4925,7 +5680,7 @@
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
@@ -4948,7 +5703,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="9"/>
+      <c r="S3" s="8"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
@@ -4973,7 +5728,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="9"/>
+      <c r="S4" s="8"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
@@ -4981,7 +5736,7 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -5004,7 +5759,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="9"/>
+      <c r="S5" s="8"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
@@ -5012,7 +5767,7 @@
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -5035,7 +5790,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="9"/>
+      <c r="S6" s="8"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -5060,7 +5815,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="9"/>
+      <c r="S7" s="8"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
@@ -5068,7 +5823,7 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
@@ -5091,7 +5846,7 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
-      <c r="S8" s="9"/>
+      <c r="S8" s="8"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
@@ -5099,7 +5854,7 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
@@ -5122,7 +5877,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="9"/>
+      <c r="S9" s="8"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
@@ -5147,7 +5902,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="9"/>
+      <c r="S10" s="8"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
@@ -5155,14 +5910,14 @@
     </row>
     <row r="11" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -5180,7 +5935,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="8"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
@@ -5188,14 +5943,14 @@
     </row>
     <row r="12" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -5213,7 +5968,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="8"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
@@ -5221,14 +5976,14 @@
     </row>
     <row r="13" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -5246,7 +6001,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="8"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
@@ -5254,14 +6009,14 @@
     </row>
     <row r="14" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -5279,7 +6034,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="8"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
@@ -5287,14 +6042,14 @@
     </row>
     <row r="15" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -5312,7 +6067,7 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="8"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
@@ -5337,21 +6092,29 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="8"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+    <row r="17" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="C17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -5362,21 +6125,29 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="8"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
+    <row r="18" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -5387,7 +6158,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="9"/>
+      <c r="S18" s="8"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
@@ -5412,7 +6183,7 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="9"/>
+      <c r="S19" s="8"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
@@ -5437,7 +6208,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="9"/>
+      <c r="S20" s="8"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -5462,7 +6233,7 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="9"/>
+      <c r="S21" s="8"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
@@ -5487,7 +6258,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="9"/>
+      <c r="S22" s="8"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
@@ -5512,7 +6283,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="9"/>
+      <c r="S23" s="8"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -5537,7 +6308,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
-      <c r="S24" s="9"/>
+      <c r="S24" s="8"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
@@ -5562,7 +6333,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="9"/>
+      <c r="S25" s="8"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
@@ -5587,7 +6358,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="9"/>
+      <c r="S26" s="8"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
@@ -5612,7 +6383,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="9"/>
+      <c r="S27" s="8"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
@@ -5637,7 +6408,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="9"/>
+      <c r="S28" s="8"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
@@ -5662,7 +6433,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="9"/>
+      <c r="S29" s="8"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
@@ -5687,7 +6458,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="9"/>
+      <c r="S30" s="8"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
@@ -5712,7 +6483,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="9"/>
+      <c r="S31" s="8"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -5737,7 +6508,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
-      <c r="S32" s="9"/>
+      <c r="S32" s="8"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
@@ -5762,7 +6533,7 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="9"/>
+      <c r="S33" s="8"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
@@ -5787,7 +6558,7 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="9"/>
+      <c r="S34" s="8"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
@@ -5812,7 +6583,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="9"/>
+      <c r="S35" s="8"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
@@ -5837,7 +6608,7 @@
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
-      <c r="S36" s="9"/>
+      <c r="S36" s="8"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
@@ -5862,7 +6633,7 @@
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
-      <c r="S37" s="9"/>
+      <c r="S37" s="8"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
@@ -5887,7 +6658,7 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
-      <c r="S38" s="9"/>
+      <c r="S38" s="8"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -5912,7 +6683,7 @@
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="9"/>
+      <c r="S39" s="8"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
@@ -5937,7 +6708,7 @@
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
-      <c r="S40" s="9"/>
+      <c r="S40" s="8"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
@@ -5962,7 +6733,7 @@
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
-      <c r="S41" s="9"/>
+      <c r="S41" s="8"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -5987,7 +6758,7 @@
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="9"/>
+      <c r="S42" s="8"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
@@ -6012,7 +6783,7 @@
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
-      <c r="S43" s="9"/>
+      <c r="S43" s="8"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
@@ -6037,7 +6808,7 @@
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
-      <c r="S44" s="9"/>
+      <c r="S44" s="8"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
@@ -6062,7 +6833,7 @@
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
-      <c r="S45" s="9"/>
+      <c r="S45" s="8"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -6087,7 +6858,7 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="9"/>
+      <c r="S46" s="8"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
@@ -6112,7 +6883,7 @@
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
-      <c r="S47" s="9"/>
+      <c r="S47" s="8"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
@@ -6137,7 +6908,7 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
-      <c r="S48" s="9"/>
+      <c r="S48" s="8"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
@@ -6162,7 +6933,7 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="9"/>
+      <c r="S49" s="8"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
@@ -6187,7 +6958,7 @@
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
-      <c r="S50" s="9"/>
+      <c r="S50" s="8"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
@@ -6212,7 +6983,7 @@
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
-      <c r="S51" s="9"/>
+      <c r="S51" s="8"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
@@ -6237,7 +7008,7 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
-      <c r="S52" s="9"/>
+      <c r="S52" s="8"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
@@ -6262,7 +7033,7 @@
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
-      <c r="S53" s="9"/>
+      <c r="S53" s="8"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
@@ -6287,7 +7058,7 @@
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
-      <c r="S54" s="9"/>
+      <c r="S54" s="8"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
@@ -6312,7 +7083,7 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
-      <c r="S55" s="9"/>
+      <c r="S55" s="8"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
@@ -6337,7 +7108,7 @@
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
-      <c r="S56" s="9"/>
+      <c r="S56" s="8"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
@@ -6362,7 +7133,7 @@
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
-      <c r="S57" s="9"/>
+      <c r="S57" s="8"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
@@ -6387,7 +7158,7 @@
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
-      <c r="S58" s="9"/>
+      <c r="S58" s="8"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
@@ -6412,7 +7183,7 @@
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
-      <c r="S59" s="9"/>
+      <c r="S59" s="8"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
@@ -6437,7 +7208,7 @@
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="9"/>
+      <c r="S60" s="8"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
@@ -6462,7 +7233,7 @@
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
-      <c r="S61" s="9"/>
+      <c r="S61" s="8"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
@@ -6487,7 +7258,7 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
-      <c r="S62" s="9"/>
+      <c r="S62" s="8"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
@@ -6512,7 +7283,7 @@
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="9"/>
+      <c r="S63" s="8"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
@@ -6537,7 +7308,7 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="9"/>
+      <c r="S64" s="8"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
@@ -6562,7 +7333,7 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="9"/>
+      <c r="S65" s="8"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
@@ -6587,7 +7358,7 @@
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
-      <c r="S66" s="9"/>
+      <c r="S66" s="8"/>
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
@@ -6612,7 +7383,7 @@
       <c r="P67" s="2"/>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
-      <c r="S67" s="9"/>
+      <c r="S67" s="8"/>
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
@@ -6637,7 +7408,7 @@
       <c r="P68" s="2"/>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
-      <c r="S68" s="9"/>
+      <c r="S68" s="8"/>
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
@@ -6662,7 +7433,7 @@
       <c r="P69" s="2"/>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
-      <c r="S69" s="9"/>
+      <c r="S69" s="8"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
@@ -6687,7 +7458,7 @@
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
-      <c r="S70" s="9"/>
+      <c r="S70" s="8"/>
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
@@ -6712,7 +7483,7 @@
       <c r="P71" s="2"/>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
-      <c r="S71" s="9"/>
+      <c r="S71" s="8"/>
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
@@ -6737,7 +7508,7 @@
       <c r="P72" s="2"/>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
-      <c r="S72" s="9"/>
+      <c r="S72" s="8"/>
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
@@ -6762,7 +7533,7 @@
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
-      <c r="S73" s="9"/>
+      <c r="S73" s="8"/>
       <c r="T73" s="2"/>
       <c r="U73" s="2"/>
       <c r="V73" s="2"/>
@@ -6787,7 +7558,7 @@
       <c r="P74" s="2"/>
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
-      <c r="S74" s="9"/>
+      <c r="S74" s="8"/>
       <c r="T74" s="2"/>
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
@@ -6812,7 +7583,7 @@
       <c r="P75" s="2"/>
       <c r="Q75" s="2"/>
       <c r="R75" s="2"/>
-      <c r="S75" s="10"/>
+      <c r="S75" s="9"/>
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
       <c r="V75" s="2"/>
@@ -6855,16 +7626,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -6873,16 +7644,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -6891,16 +7662,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -6909,13 +7680,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -6928,26 +7699,26 @@
         <v>61</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -6962,20 +7733,20 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7017,16 +7788,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -7035,16 +7806,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -7053,16 +7824,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -7071,13 +7842,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -7090,26 +7861,26 @@
         <v>61</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -7124,22 +7895,22 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7181,16 +7952,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -7199,16 +7970,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -7217,16 +7988,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -7235,13 +8006,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -7254,26 +8025,26 @@
         <v>61</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -7288,24 +8059,24 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>116</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7347,16 +8118,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -7365,7 +8136,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -7374,7 +8145,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -7383,16 +8154,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -7401,13 +8172,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -7420,26 +8191,26 @@
         <v>66</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -7454,58 +8225,58 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -7514,11 +8285,11 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -13,29 +13,25 @@
     <sheet name="Rooms" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Speakers" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Talks" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="talkTypeOfTimeslot_setup" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="talkTypeOfTimeslot_timeslotWithMatchingTalkType" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="talkTypeOfTimeslot_timeslotWithNonMatchingTalkType" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="talkHasUnavailableRoom_setup" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom_2" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom_2" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="roomConflict_setup" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="roomConflict_talksInSameRoomWithOverlappingTimeslots" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="roomConflict_talksInDifferentRoomsWithOverlappingTimeslots" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="talkWithUnavailableSpeaker_setup" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker_2" sheetId="20" state="visible" r:id="rId21"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers" sheetId="21" state="visible" r:id="rId22"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers_2" sheetId="22" state="visible" r:id="rId23"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="23" state="visible" r:id="rId24"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="24" state="visible" r:id="rId25"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_3" sheetId="25" state="visible" r:id="rId26"/>
-    <sheet name="speakerConflict_setup" sheetId="26" state="visible" r:id="rId27"/>
-    <sheet name="speakerConflict_speakerHasNoConflictingTimeslots" sheetId="27" state="visible" r:id="rId28"/>
-    <sheet name="speakerConflict_speakerHasConflictingTimeslots" sheetId="28" state="visible" r:id="rId29"/>
+    <sheet name="talkTypeOfTimeslot_timeslotWithMatchingTalkType" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="talkTypeOfTimeslot_timeslotWithNonMatchingTalkType" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="talkHasUnavailableRoom_setup" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom_2" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom_2" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="roomConflict_talksInSameRoomWithOverlappingTimeslots" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="roomConflict_talksInDifferentRoomsWithOverlappingTimeslots" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker_2" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers_2" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_3" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="speakerConflict_speakerHasNoConflictingTimeslots" sheetId="23" state="visible" r:id="rId24"/>
+    <sheet name="speakerConflict_speakerHasConflictingTimeslots" sheetId="24" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -47,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="140">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -1257,7 +1253,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1327,9 +1323,6 @@
       <c r="A7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
@@ -1346,7 +1339,6 @@
       <c r="A8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="6"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="6"/>
@@ -1363,7 +1355,9 @@
       <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="C9" s="11"/>
       <c r="D9" s="4"/>
       <c r="E9" s="11"/>
@@ -1470,7 +1464,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1556,6 +1550,9 @@
       <c r="A8" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="B8" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="6"/>
@@ -1572,9 +1569,7 @@
       <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="C9" s="11"/>
       <c r="D9" s="4"/>
       <c r="E9" s="11"/>
@@ -1681,7 +1676,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1767,9 +1762,6 @@
       <c r="A8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="6"/>
@@ -1786,7 +1778,6 @@
       <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="4"/>
       <c r="C9" s="11"/>
       <c r="D9" s="4"/>
       <c r="E9" s="11"/>
@@ -1803,7 +1794,9 @@
       <c r="A10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1843,7 +1836,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -1875,7 +1868,7 @@
         <v>133</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1893,7 +1886,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1924,10 +1917,10 @@
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -1945,10 +1938,12 @@
       <c r="B6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -1960,11 +1955,16 @@
       <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -1976,9 +1976,10 @@
       <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="6"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="6"/>
@@ -1991,41 +1992,8 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2033,9 +2001,8 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F9:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2103,7 +2070,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2175,9 +2142,12 @@
       <c r="A7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
+      <c r="B7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -2355,12 +2325,8 @@
       <c r="A7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -2377,7 +2343,9 @@
         <v>86</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
+      <c r="C8" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="D8" s="7"/>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -2417,7 +2385,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -2448,8 +2416,8 @@
       <c r="A2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>38</v>
+      <c r="B2" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -2467,7 +2435,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2498,10 +2466,10 @@
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -2519,12 +2487,10 @@
       <c r="B6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -2537,14 +2503,13 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>120</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -2555,23 +2520,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2582,7 +2531,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2600,7 +2549,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -2631,8 +2580,8 @@
       <c r="A2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>38</v>
+      <c r="B2" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -2681,10 +2630,10 @@
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -2702,12 +2651,10 @@
       <c r="B6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -2720,11 +2667,12 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -2735,25 +2683,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2764,7 +2694,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2902,8 +2832,9 @@
       <c r="A7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="B7" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -3064,10 +2995,10 @@
       <c r="A7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="6"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -3412,7 +3343,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3482,8 +3413,8 @@
       <c r="A7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>121</v>
+      <c r="B7" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
@@ -3575,7 +3506,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3646,7 +3577,7 @@
         <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
@@ -3738,7 +3669,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3808,9 +3739,8 @@
       <c r="A7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
-        <v>122</v>
+      <c r="B7" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
@@ -3884,7 +3814,7 @@
         <v>133</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3902,7 +3832,7 @@
         <v>134</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3933,495 +3863,6 @@
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C5" s="4"/>
@@ -4463,9 +3904,13 @@
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -4499,175 +3944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <tabColor rgb="FF00DCFF"/>
@@ -7735,7 +7012,9 @@
       <c r="A7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
@@ -7900,7 +7179,9 @@
       <c r="B7" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -7941,7 +7222,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -7972,8 +7253,8 @@
       <c r="A2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>33</v>
+      <c r="B2" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -8022,7 +7303,7 @@
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="11"/>
@@ -8059,14 +7340,10 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>116</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -8078,9 +7355,57 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+    </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8088,8 +7413,9 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F9:H9"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -8227,7 +7553,9 @@
       <c r="A7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -15,23 +15,17 @@
     <sheet name="Talks" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="talkTypeOfTimeslot_timeslotWithMatchingTalkType" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="talkTypeOfTimeslot_timeslotWithNonMatchingTalkType" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="talkHasUnavailableRoom_setup" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom_2" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom_2" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="roomConflict_talksInSameRoomWithOverlappingTimeslots" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="roomConflict_talksInDifferentRoomsWithOverlappingTimeslots" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker_2" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers_2" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="20" state="visible" r:id="rId21"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="21" state="visible" r:id="rId22"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_3" sheetId="22" state="visible" r:id="rId23"/>
-    <sheet name="speakerConflict_speakerHasNoConflictingTimeslots" sheetId="23" state="visible" r:id="rId24"/>
-    <sheet name="speakerConflict_speakerHasConflictingTimeslots" sheetId="24" state="visible" r:id="rId25"/>
+    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="roomConflict_talksInSameRoomWithOverlappingTimeslots" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="roomConflict_talksInDifferentRoomsWithOverlappingTimeslots" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="speakerConflict_speakerHasNoConflictingTimeslots" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="speakerConflict_speakerHasConflictingTimeslots" sheetId="18" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="118">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -237,113 +231,45 @@
     <t xml:space="preserve">10:00</t>
   </si>
   <si>
-    <t xml:space="preserve">talkTypeOfTimeslot_talkType1</t>
+    <t xml:space="preserve">normalTalkType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nonMatchingTalkType</t>
   </si>
   <si>
     <t xml:space="preserve">11:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Tue 2018-01-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_talkType1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wed 2018-01-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roomConflict_talkType1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 2018-01-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_talkType1</t>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:00-10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:30-10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00-11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">normalRoom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">normalRoom2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unavailableRoom</t>
   </si>
   <si>
     <t xml:space="preserve">Fri 2018-01-05</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">speakerConflict</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_talkType1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:00-10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:00-11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:30-10:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkTypeOfTimeslot_room1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_room1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_room2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_room3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_room4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roomConflict_room1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roomConflict_room2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_room1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">speakerConflict</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_room1</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Required timeslot tags</t>
   </si>
   <si>
@@ -368,35 +294,16 @@
     <t xml:space="preserve">Undesired room tags</t>
   </si>
   <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_speaker4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">speakerConflict</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_speaker1</t>
-    </r>
+    <t xml:space="preserve">Amy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarah</t>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -438,132 +345,28 @@
     <t xml:space="preserve">Room</t>
   </si>
   <si>
-    <t xml:space="preserve">talkTypeOfTimeslot_talk1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkTypeOfTimeslot_talk2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_talk1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkHasUnavailableRoom_talk2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roomConflict_talk1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roomConflict_talk2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_talk1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_talk2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker1, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_talk3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_talk4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker2, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">talkWithUnavailableSpeaker_talk5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker3, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">talkWithUnavailableSpeaker_speaker4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">speakerConflict</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_talk1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">speakerConflict</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_talk2</t>
-    </r>
+    <t xml:space="preserve">normalTalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">normalTalk2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy, John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeakerPaul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy, Paul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithUnavailableSpeakerPaulAndSarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul, Sarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talkWithSameSpeakerAsNormalTalk</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint package</t>
@@ -588,9 +391,6 @@
   </si>
   <si>
     <t xml:space="preserve">-1hard/0soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">speakerConflict_talk1</t>
   </si>
 </sst>
 </file>
@@ -714,19 +514,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -747,10 +551,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1203,7 +1003,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -1214,16 +1014,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1232,16 +1032,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1250,16 +1050,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>136</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1268,13 +1068,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1283,110 +1083,68 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
+      <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1394,9 +1152,8 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F9:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1414,7 +1171,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -1425,16 +1182,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1443,16 +1200,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1461,16 +1218,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1479,13 +1236,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1494,111 +1251,67 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
+      <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1606,9 +1319,8 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F9:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1626,7 +1338,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -1637,16 +1349,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1655,16 +1367,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1673,16 +1385,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>136</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1691,13 +1403,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1706,109 +1418,82 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
+      <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1816,9 +1501,8 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F9:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1836,7 +1520,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -1847,16 +1531,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1865,16 +1549,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>38</v>
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1883,16 +1567,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1901,13 +1585,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1916,82 +1600,63 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2020,7 +1685,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -2031,16 +1696,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2049,16 +1714,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>38</v>
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2067,16 +1732,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>137</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2085,13 +1750,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2100,81 +1765,64 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
+        <v>73</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2203,7 +1851,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -2214,16 +1862,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2232,16 +1880,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>38</v>
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2250,16 +1898,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>117</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2268,13 +1916,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2283,80 +1931,63 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
+        <v>105</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2396,16 +2027,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2414,16 +2045,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2432,16 +2063,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>117</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2450,13 +2081,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2465,60 +2096,61 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+        <v>107</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2531,7 +2163,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2560,16 +2192,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2578,16 +2210,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2596,16 +2228,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2614,13 +2246,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2629,59 +2261,64 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>71</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+        <v>73</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2694,7 +2331,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2712,7 +2349,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -2723,16 +2360,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2741,16 +2378,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2759,16 +2396,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>117</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2777,13 +2414,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2792,61 +2429,80 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>71</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>102</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2857,171 +2513,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -3065,7 +2557,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
@@ -3080,1027 +2572,53 @@
       </c>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00DCFF"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4116,48 +2634,31 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="4" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="16" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1014" min="7" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1015" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>59</v>
@@ -4166,45 +2667,18 @@
         <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>64</v>
@@ -4212,246 +2686,43 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>67</v>
-      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>67</v>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:O1"/>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4468,8 +2739,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.7"/>
@@ -4480,8 +2751,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="10" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="22" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="10" style="0" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1018" min="16" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1019" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4494,321 +2766,144 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>85</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>86</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>88</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:U1"/>
+  <mergeCells count="2">
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4829,8 +2924,8 @@
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="39.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="31.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.63"/>
@@ -4855,64 +2950,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -4921,18 +3016,20 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -4949,21 +3046,23 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="8"/>
+      <c r="S2" s="9"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -4980,7 +3079,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="8"/>
+      <c r="S3" s="9"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
@@ -5005,21 +3104,23 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="8"/>
+      <c r="S4" s="9"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -5036,21 +3137,23 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="8"/>
+      <c r="S5" s="9"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>118</v>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -5067,7 +3170,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="8"/>
+      <c r="S6" s="9"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -5092,21 +3195,23 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="8"/>
+      <c r="S7" s="9"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -5123,27 +3228,21 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
-      <c r="S8" s="8"/>
+      <c r="S8" s="9"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>120</v>
-      </c>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -5154,7 +3253,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="8"/>
+      <c r="S9" s="9"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
@@ -5179,29 +3278,21 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="8"/>
+      <c r="S10" s="9"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>121</v>
-      </c>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -5212,29 +3303,21 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
-      <c r="S11" s="8"/>
+      <c r="S11" s="9"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>122</v>
-      </c>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>123</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -5245,29 +3328,21 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="8"/>
+      <c r="S12" s="9"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>124</v>
-      </c>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -5278,29 +3353,21 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="8"/>
+      <c r="S13" s="9"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>125</v>
-      </c>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>126</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -5311,29 +3378,21 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="8"/>
+      <c r="S14" s="9"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>127</v>
-      </c>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>128</v>
-      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -5344,7 +3403,7 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="8"/>
+      <c r="S15" s="9"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
@@ -5369,29 +3428,21 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="8"/>
+      <c r="S16" s="9"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>129</v>
-      </c>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -5402,29 +3453,21 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="8"/>
+      <c r="S17" s="9"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>130</v>
-      </c>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -5435,7 +3478,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="8"/>
+      <c r="S18" s="9"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
@@ -5460,7 +3503,7 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="8"/>
+      <c r="S19" s="9"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
@@ -5485,7 +3528,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="8"/>
+      <c r="S20" s="9"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -5510,7 +3553,7 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="8"/>
+      <c r="S21" s="9"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
@@ -5535,7 +3578,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="8"/>
+      <c r="S22" s="9"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
@@ -5560,7 +3603,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="8"/>
+      <c r="S23" s="9"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -5585,7 +3628,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
-      <c r="S24" s="8"/>
+      <c r="S24" s="9"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
@@ -5610,7 +3653,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="8"/>
+      <c r="S25" s="9"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
@@ -5635,7 +3678,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="8"/>
+      <c r="S26" s="9"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
@@ -5660,7 +3703,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="8"/>
+      <c r="S27" s="9"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
@@ -5685,7 +3728,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="8"/>
+      <c r="S28" s="9"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
@@ -5710,7 +3753,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="8"/>
+      <c r="S29" s="9"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
@@ -5735,7 +3778,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="8"/>
+      <c r="S30" s="9"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
@@ -5760,7 +3803,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="8"/>
+      <c r="S31" s="9"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -5785,7 +3828,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
-      <c r="S32" s="8"/>
+      <c r="S32" s="9"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
@@ -5810,7 +3853,7 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="8"/>
+      <c r="S33" s="9"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
@@ -5835,7 +3878,7 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="8"/>
+      <c r="S34" s="9"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
@@ -5860,7 +3903,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="8"/>
+      <c r="S35" s="9"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
@@ -5885,7 +3928,7 @@
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
-      <c r="S36" s="8"/>
+      <c r="S36" s="9"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
@@ -5910,7 +3953,7 @@
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
-      <c r="S37" s="8"/>
+      <c r="S37" s="9"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
@@ -5935,7 +3978,7 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
-      <c r="S38" s="8"/>
+      <c r="S38" s="9"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -5960,7 +4003,7 @@
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="8"/>
+      <c r="S39" s="9"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
@@ -5985,7 +4028,7 @@
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
-      <c r="S40" s="8"/>
+      <c r="S40" s="9"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
@@ -6010,7 +4053,7 @@
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
-      <c r="S41" s="8"/>
+      <c r="S41" s="9"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -6035,7 +4078,7 @@
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="8"/>
+      <c r="S42" s="9"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
@@ -6060,7 +4103,7 @@
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
-      <c r="S43" s="8"/>
+      <c r="S43" s="9"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
@@ -6085,7 +4128,7 @@
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
-      <c r="S44" s="8"/>
+      <c r="S44" s="9"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
@@ -6110,7 +4153,7 @@
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
-      <c r="S45" s="8"/>
+      <c r="S45" s="9"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -6135,7 +4178,7 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="8"/>
+      <c r="S46" s="9"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
@@ -6160,7 +4203,7 @@
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
-      <c r="S47" s="8"/>
+      <c r="S47" s="9"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
@@ -6185,7 +4228,7 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
-      <c r="S48" s="8"/>
+      <c r="S48" s="9"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
@@ -6210,7 +4253,7 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="8"/>
+      <c r="S49" s="9"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
@@ -6235,7 +4278,7 @@
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
-      <c r="S50" s="8"/>
+      <c r="S50" s="9"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
@@ -6260,7 +4303,7 @@
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
-      <c r="S51" s="8"/>
+      <c r="S51" s="9"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
@@ -6285,7 +4328,7 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
-      <c r="S52" s="8"/>
+      <c r="S52" s="9"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
@@ -6310,7 +4353,7 @@
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
-      <c r="S53" s="8"/>
+      <c r="S53" s="9"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
@@ -6335,7 +4378,7 @@
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
-      <c r="S54" s="8"/>
+      <c r="S54" s="9"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
@@ -6360,7 +4403,7 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
-      <c r="S55" s="8"/>
+      <c r="S55" s="9"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
@@ -6385,7 +4428,7 @@
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
-      <c r="S56" s="8"/>
+      <c r="S56" s="9"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
@@ -6410,7 +4453,7 @@
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
-      <c r="S57" s="8"/>
+      <c r="S57" s="9"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
@@ -6435,7 +4478,7 @@
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="9"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
@@ -6460,7 +4503,7 @@
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
-      <c r="S59" s="8"/>
+      <c r="S59" s="9"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
@@ -6485,7 +4528,7 @@
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="8"/>
+      <c r="S60" s="9"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
@@ -6510,7 +4553,7 @@
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
-      <c r="S61" s="8"/>
+      <c r="S61" s="9"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
@@ -6535,7 +4578,7 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
-      <c r="S62" s="8"/>
+      <c r="S62" s="9"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
@@ -6560,7 +4603,7 @@
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="8"/>
+      <c r="S63" s="9"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
@@ -6585,7 +4628,7 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="8"/>
+      <c r="S64" s="9"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
@@ -6610,263 +4653,23 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="8"/>
+      <c r="S65" s="10"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="8"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="8"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="8"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="8"/>
-      <c r="T69" s="2"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="8"/>
-      <c r="T70" s="2"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="2"/>
-      <c r="W70" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="8"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="8"/>
-      <c r="T73" s="2"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="8"/>
-      <c r="T74" s="2"/>
-      <c r="U74" s="2"/>
-      <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6903,16 +4706,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -6921,16 +4724,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -6939,16 +4742,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -6957,13 +4760,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -6972,60 +4775,62 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7038,7 +4843,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -7067,16 +4872,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -7085,16 +4890,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -7103,16 +4908,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -7121,13 +4926,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -7136,62 +4941,62 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="A7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7204,7 +5009,7 @@
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -7222,7 +5027,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -7233,16 +5038,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -7251,7 +5056,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -7260,7 +5065,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -7269,16 +5074,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -7287,13 +5092,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -7302,110 +5107,66 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
+      <c r="A7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7413,9 +5174,8 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F9:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -7433,7 +5193,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -7444,16 +5204,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -7462,7 +5222,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -7471,7 +5231,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -7480,16 +5240,16 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>135</v>
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -7498,13 +5258,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -7513,112 +5273,65 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
+      <c r="A7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7626,9 +5339,8 @@
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F9:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="117">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t xml:space="preserve">unavailableRoom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fri 2018-01-05</t>
   </si>
   <si>
     <t xml:space="preserve">Required timeslot tags</t>
@@ -518,11 +515,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1014,10 +1011,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1032,7 +1029,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -1050,10 +1047,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1100,7 +1097,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -1125,20 +1122,20 @@
       <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -1182,10 +1179,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1200,7 +1197,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -1218,10 +1215,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1268,7 +1265,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -1293,19 +1290,19 @@
       <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -1349,10 +1346,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1367,7 +1364,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>38</v>
@@ -1385,10 +1382,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1435,7 +1432,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -1461,15 +1458,15 @@
         <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -1477,18 +1474,18 @@
       <c r="A8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-      <c r="K8" s="4"/>
+      <c r="K8" s="5"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
@@ -1531,10 +1528,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1549,7 +1546,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>40</v>
@@ -1567,10 +1564,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1617,7 +1614,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -1643,16 +1640,16 @@
         <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -1696,10 +1693,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1714,7 +1711,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>40</v>
@@ -1732,10 +1729,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1782,7 +1779,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -1809,16 +1806,16 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -1862,10 +1859,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1880,7 +1877,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>40</v>
@@ -1898,10 +1895,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1948,7 +1945,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -1974,16 +1971,16 @@
         <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -2027,10 +2024,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2043,9 +2040,9 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>40</v>
@@ -2063,10 +2060,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2113,7 +2110,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -2139,16 +2136,16 @@
         <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -2192,10 +2189,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2210,7 +2207,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>42</v>
@@ -2228,10 +2225,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2278,7 +2275,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -2304,19 +2301,19 @@
         <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -2360,10 +2357,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2378,7 +2375,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>42</v>
@@ -2396,10 +2393,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2446,7 +2443,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -2472,15 +2469,15 @@
         <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -2488,18 +2485,18 @@
       <c r="A8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-      <c r="K8" s="4"/>
+      <c r="K8" s="5"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
@@ -2634,7 +2631,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
@@ -2700,25 +2697,17 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+    <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2771,9 +2760,7 @@
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
@@ -2782,28 +2769,28 @@
         <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>70</v>
@@ -2814,19 +2801,13 @@
       <c r="L2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2837,15 +2818,15 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2856,15 +2837,15 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2875,15 +2856,15 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2950,64 +2931,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -3016,19 +2997,19 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -3054,14 +3035,14 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3085,15 +3066,23 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -3110,16 +3099,16 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -3143,16 +3132,16 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -3200,39 +3189,6 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -4706,10 +4662,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -4724,7 +4680,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>33</v>
@@ -4742,10 +4698,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -4792,7 +4748,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -4818,17 +4774,17 @@
         <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -4872,10 +4828,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -4890,7 +4846,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>33</v>
@@ -4908,10 +4864,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -4958,7 +4914,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -4980,21 +4936,21 @@
       <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -5038,10 +4994,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -5056,7 +5012,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -5074,10 +5030,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -5124,7 +5080,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -5146,21 +5102,21 @@
       <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
@@ -5204,10 +5160,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -5222,7 +5178,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>36</v>
@@ -5240,10 +5196,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -5290,7 +5246,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>70</v>
@@ -5312,20 +5268,20 @@
       <c r="M6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>102</v>
+      <c r="C7" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -398,7 +398,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -428,20 +428,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="4">
@@ -498,7 +488,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -515,23 +505,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -543,19 +521,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1013,14 +983,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1031,14 +1001,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1049,14 +1019,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1065,13 +1035,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1085,15 +1055,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1102,42 +1072,42 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1181,14 +1151,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1199,14 +1169,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1217,14 +1187,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>115</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1233,13 +1203,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1253,15 +1223,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1270,41 +1240,41 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1348,14 +1318,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1366,14 +1336,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1384,14 +1354,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1400,13 +1370,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1420,15 +1390,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1437,21 +1407,21 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1460,34 +1430,34 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1530,14 +1500,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1548,14 +1518,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1566,14 +1536,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1582,13 +1552,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1602,15 +1572,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1619,21 +1589,21 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1642,16 +1612,16 @@
       <c r="C7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1695,14 +1665,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1713,14 +1683,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1731,14 +1701,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1747,13 +1717,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1767,15 +1737,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1784,21 +1754,21 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1808,16 +1778,16 @@
       <c r="C7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1861,14 +1831,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1879,14 +1849,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1897,14 +1867,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1913,13 +1883,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1933,15 +1903,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1950,21 +1920,21 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1973,16 +1943,16 @@
       <c r="B7" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2026,14 +1996,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2044,14 +2014,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2062,14 +2032,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2078,13 +2048,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2098,15 +2068,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -2115,21 +2085,21 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -2138,16 +2108,16 @@
       <c r="B7" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2191,14 +2161,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2209,14 +2179,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2227,14 +2197,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2243,13 +2213,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2263,15 +2233,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -2286,15 +2256,15 @@
       <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -2303,19 +2273,19 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2359,14 +2329,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2377,14 +2347,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2395,14 +2365,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2411,13 +2381,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2431,15 +2401,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -2454,15 +2424,15 @@
       <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -2471,34 +2441,34 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2698,16 +2668,16 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2795,10 +2765,10 @@
       <c r="J2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="1" t="s">
         <v>72</v>
       </c>
       <c r="M2" s="1"/>
@@ -2809,77 +2779,77 @@
       <c r="A3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3001,7 +2971,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B2" s="2"/>
@@ -3027,7 +2997,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="9"/>
+      <c r="S2" s="6"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
@@ -3060,7 +3030,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="9"/>
+      <c r="S3" s="6"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
@@ -3093,7 +3063,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="9"/>
+      <c r="S4" s="6"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
@@ -3126,7 +3096,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="9"/>
+      <c r="S5" s="6"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
@@ -3159,7 +3129,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="9"/>
+      <c r="S6" s="6"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -3184,7 +3154,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="9"/>
+      <c r="S7" s="6"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
@@ -3209,7 +3179,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="9"/>
+      <c r="S9" s="6"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
@@ -3234,7 +3204,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="9"/>
+      <c r="S10" s="6"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
@@ -3259,7 +3229,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="6"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
@@ -3284,7 +3254,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="6"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
@@ -3309,7 +3279,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="6"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
@@ -3334,7 +3304,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="6"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
@@ -3359,7 +3329,7 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="6"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
@@ -3384,7 +3354,7 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="6"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
@@ -3409,7 +3379,7 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="6"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -3434,7 +3404,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="9"/>
+      <c r="S18" s="6"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
@@ -3459,7 +3429,7 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="9"/>
+      <c r="S19" s="6"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
@@ -3484,7 +3454,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="9"/>
+      <c r="S20" s="6"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -3509,7 +3479,7 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="9"/>
+      <c r="S21" s="6"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
@@ -3534,7 +3504,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="9"/>
+      <c r="S22" s="6"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
@@ -3559,7 +3529,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="9"/>
+      <c r="S23" s="6"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -3584,7 +3554,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
-      <c r="S24" s="9"/>
+      <c r="S24" s="6"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
@@ -3609,7 +3579,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="9"/>
+      <c r="S25" s="6"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
@@ -3634,7 +3604,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="9"/>
+      <c r="S26" s="6"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
@@ -3659,7 +3629,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="9"/>
+      <c r="S27" s="6"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
@@ -3684,7 +3654,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="9"/>
+      <c r="S28" s="6"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
@@ -3709,7 +3679,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="9"/>
+      <c r="S29" s="6"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
@@ -3734,7 +3704,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="9"/>
+      <c r="S30" s="6"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
@@ -3759,7 +3729,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="9"/>
+      <c r="S31" s="6"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -3784,7 +3754,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
-      <c r="S32" s="9"/>
+      <c r="S32" s="6"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
@@ -3809,7 +3779,7 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="9"/>
+      <c r="S33" s="6"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
@@ -3834,7 +3804,7 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="9"/>
+      <c r="S34" s="6"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
@@ -3859,7 +3829,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="9"/>
+      <c r="S35" s="6"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
@@ -3884,7 +3854,7 @@
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
-      <c r="S36" s="9"/>
+      <c r="S36" s="6"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
@@ -3909,7 +3879,7 @@
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
-      <c r="S37" s="9"/>
+      <c r="S37" s="6"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
@@ -3934,7 +3904,7 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
-      <c r="S38" s="9"/>
+      <c r="S38" s="6"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -3959,7 +3929,7 @@
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="9"/>
+      <c r="S39" s="6"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
@@ -3984,7 +3954,7 @@
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
-      <c r="S40" s="9"/>
+      <c r="S40" s="6"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
@@ -4009,7 +3979,7 @@
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
-      <c r="S41" s="9"/>
+      <c r="S41" s="6"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -4034,7 +4004,7 @@
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="9"/>
+      <c r="S42" s="6"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
@@ -4059,7 +4029,7 @@
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
-      <c r="S43" s="9"/>
+      <c r="S43" s="6"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
@@ -4084,7 +4054,7 @@
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
-      <c r="S44" s="9"/>
+      <c r="S44" s="6"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
@@ -4109,7 +4079,7 @@
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
-      <c r="S45" s="9"/>
+      <c r="S45" s="6"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -4134,7 +4104,7 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="9"/>
+      <c r="S46" s="6"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
@@ -4159,7 +4129,7 @@
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
-      <c r="S47" s="9"/>
+      <c r="S47" s="6"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
@@ -4184,7 +4154,7 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
-      <c r="S48" s="9"/>
+      <c r="S48" s="6"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
@@ -4209,7 +4179,7 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="9"/>
+      <c r="S49" s="6"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
@@ -4234,7 +4204,7 @@
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
-      <c r="S50" s="9"/>
+      <c r="S50" s="6"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
@@ -4259,7 +4229,7 @@
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
-      <c r="S51" s="9"/>
+      <c r="S51" s="6"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
@@ -4284,7 +4254,7 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
-      <c r="S52" s="9"/>
+      <c r="S52" s="6"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
@@ -4309,7 +4279,7 @@
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
-      <c r="S53" s="9"/>
+      <c r="S53" s="6"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
@@ -4334,7 +4304,7 @@
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
-      <c r="S54" s="9"/>
+      <c r="S54" s="6"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
@@ -4359,7 +4329,7 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
-      <c r="S55" s="9"/>
+      <c r="S55" s="6"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
@@ -4384,7 +4354,7 @@
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
-      <c r="S56" s="9"/>
+      <c r="S56" s="6"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
@@ -4409,7 +4379,7 @@
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
-      <c r="S57" s="9"/>
+      <c r="S57" s="6"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
@@ -4434,7 +4404,7 @@
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
-      <c r="S58" s="9"/>
+      <c r="S58" s="6"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
@@ -4459,7 +4429,7 @@
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
-      <c r="S59" s="9"/>
+      <c r="S59" s="6"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
@@ -4484,7 +4454,7 @@
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="9"/>
+      <c r="S60" s="6"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
@@ -4509,7 +4479,7 @@
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
-      <c r="S61" s="9"/>
+      <c r="S61" s="6"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
@@ -4534,7 +4504,7 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
-      <c r="S62" s="9"/>
+      <c r="S62" s="6"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
@@ -4559,7 +4529,7 @@
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="9"/>
+      <c r="S63" s="6"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
@@ -4584,7 +4554,7 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="9"/>
+      <c r="S64" s="6"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
@@ -4609,7 +4579,7 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="10"/>
+      <c r="S65" s="7"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
@@ -4664,14 +4634,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4682,14 +4652,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4700,14 +4670,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4716,13 +4686,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4736,15 +4706,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -4753,21 +4723,21 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -4776,17 +4746,17 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4830,14 +4800,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4848,14 +4818,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4866,14 +4836,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4882,13 +4852,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -4902,15 +4872,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -4919,40 +4889,40 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="13"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4996,14 +4966,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -5014,14 +4984,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -5032,14 +5002,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5048,13 +5018,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -5068,15 +5038,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -5085,40 +5055,40 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5162,14 +5132,14 @@
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="12"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -5180,14 +5150,14 @@
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -5198,14 +5168,14 @@
       <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5214,13 +5184,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="B4" s="12"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -5234,15 +5204,15 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -5251,39 +5221,39 @@
       <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Rooms" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Speakers" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Talks" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="talkTypeOfTimeslot_timeslotWithMatchingTalkType" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="talkTypeOfTimeslot_timeslotWithNonMatchingTalkType" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Talk type of timeslot 1" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Talk type of timeslot 2" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="8" state="visible" r:id="rId9"/>
     <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="9" state="visible" r:id="rId10"/>
     <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="10" state="visible" r:id="rId11"/>
@@ -4621,7 +4621,7 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
@@ -4767,6 +4767,7 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B5:D5"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -15,17 +15,17 @@
     <sheet name="Talks" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="Talk type of timeslot 1" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="Talk type of timeslot 2" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="talkHasUnavailableRoom_talkWithAvailableRoom" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="talkHasUnavailableRoom_talkWithUnavailableRoom" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="roomConflict_talksInSameRoomWithoutOverlappingTimeslots" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="roomConflict_talksInSameRoomWithOverlappingTimeslots" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="roomConflict_talksInDifferentRoomsWithOverlappingTimeslots" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableSpeaker" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithoutUnavailableTwoSpeakers" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="talkWithUnavailableSpeaker_talkWithOneOrMoreUnavailableSpeaker_2" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="speakerConflict_speakerHasNoConflictingTimeslots" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="speakerConflict_speakerHasConflictingTimeslots" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="Room unavailable timeslot 1" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Room unavailable timeslot 2" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Room conflict 1" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Room conflict 2" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="Room conflict 3" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="Speaker unavailable timeslot 1" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="Speaker unavailable timeslot 2" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="Speaker unavailable timeslot 3" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="Speaker unavailable timeslot 4" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="Speaker unavailable timeslot 5" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="Speaker conflict" sheetId="18" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="129">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -231,7 +231,7 @@
     <t xml:space="preserve">10:00</t>
   </si>
   <si>
-    <t xml:space="preserve">normalTalkType</t>
+    <t xml:space="preserve">Normal talk type</t>
   </si>
   <si>
     <t xml:space="preserve">09:30</t>
@@ -240,7 +240,7 @@
     <t xml:space="preserve">10:30</t>
   </si>
   <si>
-    <t xml:space="preserve">nonMatchingTalkType</t>
+    <t xml:space="preserve">Non matching talk type</t>
   </si>
   <si>
     <t xml:space="preserve">11:00</t>
@@ -258,13 +258,13 @@
     <t xml:space="preserve">10:00-11:00</t>
   </si>
   <si>
-    <t xml:space="preserve">normalRoom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normalRoom2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unavailableRoom</t>
+    <t xml:space="preserve">Normal room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal room 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unavailable room</t>
   </si>
   <si>
     <t xml:space="preserve">Required timeslot tags</t>
@@ -342,28 +342,28 @@
     <t xml:space="preserve">Room</t>
   </si>
   <si>
-    <t xml:space="preserve">normalTalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normalTalk2</t>
+    <t xml:space="preserve">Normal talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal talk 2</t>
   </si>
   <si>
     <t xml:space="preserve">Amy, John</t>
   </si>
   <si>
-    <t xml:space="preserve">talkWithUnavailableSpeakerPaul</t>
+    <t xml:space="preserve">Talk with unavailable speaker Paul</t>
   </si>
   <si>
     <t xml:space="preserve">Amy, Paul</t>
   </si>
   <si>
-    <t xml:space="preserve">talkWithUnavailableSpeakerPaulAndSarah</t>
+    <t xml:space="preserve">Talk with unavailable speaker Paul and Sarah</t>
   </si>
   <si>
     <t xml:space="preserve">Paul, Sarah</t>
   </si>
   <si>
-    <t xml:space="preserve">talkWithSameSpeakerAsNormalTalk</t>
+    <t xml:space="preserve">Talk with same speaker as normal talk</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint package</t>
@@ -375,19 +375,55 @@
     <t xml:space="preserve">Constraint name</t>
   </si>
   <si>
+    <t xml:space="preserve">Timeslot with matching talk type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Score</t>
   </si>
   <si>
     <t xml:space="preserve">0hard/0soft</t>
   </si>
   <si>
+    <t xml:space="preserve">Timeslot with non matching talk type</t>
+  </si>
+  <si>
     <t xml:space="preserve">-10000hard/0soft</t>
   </si>
   <si>
+    <t xml:space="preserve">Talk with available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with unavailable room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talks in same room without overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talks in same room with overlapping timeslots</t>
+  </si>
+  <si>
     <t xml:space="preserve">-10hard/0soft</t>
   </si>
   <si>
+    <t xml:space="preserve">Talks in different rooms with overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk without unavailable speaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk without unavailable two speakers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with one or more unavailable speaker</t>
+  </si>
+  <si>
     <t xml:space="preserve">-1hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speaker has no conflicting timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speaker has conflicting timeslots</t>
   </si>
 </sst>
 </file>
@@ -463,7 +499,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -487,8 +523,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,12 +540,12 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -521,22 +560,59 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
     <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
     <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Test" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -634,183 +710,183 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>100</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -821,7 +897,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
@@ -832,7 +908,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -843,7 +919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -854,7 +930,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -865,7 +941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
@@ -876,7 +952,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -887,7 +963,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -898,7 +974,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
@@ -909,7 +985,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
@@ -920,7 +996,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>52</v>
       </c>
@@ -931,7 +1007,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>54</v>
       </c>
@@ -942,7 +1018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>55</v>
       </c>
@@ -970,146 +1046,163 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2" t="s">
+      <c r="C8" s="15"/>
+      <c r="D8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1118,9 +1211,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1138,145 +1232,162 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1285,9 +1396,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1305,161 +1417,178 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1467,9 +1596,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1487,143 +1617,160 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1632,9 +1779,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1652,144 +1800,161 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1798,9 +1963,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1818,143 +1984,160 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1963,9 +2146,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1983,143 +2167,160 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2128,9 +2329,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2148,146 +2350,163 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="B2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2" t="s">
+      <c r="C8" s="0"/>
+      <c r="D8" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2296,9 +2515,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2316,161 +2536,178 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2478,9 +2715,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2617,11 +2855,11 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -2667,7 +2905,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>75</v>
       </c>
@@ -2675,9 +2913,9 @@
         <v>64</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
+      <c r="F5" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2725,14 +2963,14 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -2788,8 +3026,8 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2807,8 +3045,8 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2826,8 +3064,8 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2984,9 +3222,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -3017,9 +3253,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -3036,7 +3270,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>104</v>
       </c>
@@ -3050,9 +3284,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -3069,7 +3301,7 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>106</v>
       </c>
@@ -3083,9 +3315,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3102,7 +3332,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>108</v>
       </c>
@@ -3116,9 +3346,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -4621,144 +4849,161 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="16.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4767,10 +5012,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4788,45 +5033,45 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -4834,17 +5079,17 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>114</v>
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
+      <c r="H3" s="17"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -4852,80 +5097,97 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>116</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4934,9 +5196,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4954,144 +5217,161 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5100,9 +5380,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5120,143 +5401,160 @@
     <tabColor rgb="FF00DCFF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5265,9 +5563,10 @@
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="16"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -715,7 +715,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -726,7 +726,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
@@ -748,7 +748,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -770,7 +770,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -781,7 +781,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -792,7 +792,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -803,7 +803,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -814,7 +814,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -825,7 +825,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
@@ -836,7 +836,7 @@
         <v>26</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -847,7 +847,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -858,7 +858,7 @@
         <v>29</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -869,7 +869,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -880,7 +880,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Conference name</t>
   </si>
   <si>
-    <t xml:space="preserve">JayFocus 2023</t>
+    <t xml:space="preserve">Junit test</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint</t>
@@ -691,7 +691,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="4" style="0" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="128">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -141,10 +141,13 @@
     <t xml:space="preserve">Talk type of timeslot</t>
   </si>
   <si>
-    <t xml:space="preserve">n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard penalty per talk in a timeslot with an other talk type</t>
+    <t xml:space="preserve">Hard penalty per talk in a timeslot with another talk type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk type of room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard penalty per talk in a room with another talk type</t>
   </si>
   <si>
     <t xml:space="preserve">Room unavailable timeslot</t>
@@ -387,7 +390,7 @@
     <t xml:space="preserve">Timeslot with non matching talk type</t>
   </si>
   <si>
-    <t xml:space="preserve">-10000hard/0soft</t>
+    <t xml:space="preserve">-1hard/0soft</t>
   </si>
   <si>
     <t xml:space="preserve">Talk with available room</t>
@@ -402,9 +405,6 @@
     <t xml:space="preserve">Talks in same room with overlapping timeslots</t>
   </si>
   <si>
-    <t xml:space="preserve">-10hard/0soft</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talks in different rooms with overlapping timeslots</t>
   </si>
   <si>
@@ -415,9 +415,6 @@
   </si>
   <si>
     <t xml:space="preserve">Talk with one or more unavailable speaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1hard/0soft</t>
   </si>
   <si>
     <t xml:space="preserve">Speaker has no conflicting timeslots</t>
@@ -580,7 +577,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -612,7 +609,7 @@
     <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Test" xfId="20" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -682,7 +679,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.7"/>
@@ -890,143 +887,154 @@
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>34</v>
+      <c r="B29" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>34</v>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>34</v>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1057,10 +1065,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1075,10 +1083,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1096,7 +1104,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1111,10 +1119,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1145,7 +1153,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1161,16 +1169,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1184,14 +1192,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1243,10 +1251,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1261,10 +1269,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1282,7 +1290,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1297,10 +1305,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1331,7 +1339,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1347,16 +1355,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1370,13 +1378,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1428,10 +1436,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1446,10 +1454,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1482,10 +1490,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1516,7 +1524,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1532,16 +1540,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1555,10 +1563,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1572,11 +1580,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -1628,10 +1636,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1646,10 +1654,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1682,10 +1690,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1716,7 +1724,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1732,16 +1740,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1755,10 +1763,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -1811,10 +1819,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1829,10 +1837,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1865,10 +1873,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1899,7 +1907,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1915,16 +1923,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1938,11 +1946,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -1995,10 +2003,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2013,10 +2021,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2049,10 +2057,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2083,7 +2091,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2099,16 +2107,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2122,10 +2130,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2178,10 +2186,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2196,10 +2204,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2232,10 +2240,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2266,7 +2274,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2282,16 +2290,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2305,10 +2313,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2361,10 +2369,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2379,10 +2387,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2400,7 +2408,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2415,10 +2423,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2449,7 +2457,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2465,16 +2473,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2488,14 +2496,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -2547,10 +2555,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2565,10 +2573,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2586,7 +2594,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2601,10 +2609,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2635,7 +2643,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2651,16 +2659,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2674,10 +2682,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -2691,11 +2699,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -2747,63 +2755,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -2856,37 +2864,37 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2895,10 +2903,10 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2907,10 +2915,10 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
@@ -2964,7 +2972,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2974,40 +2982,40 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -3015,7 +3023,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3034,7 +3042,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3053,7 +3061,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -3072,7 +3080,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3139,85 +3147,85 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -3241,14 +3249,14 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3272,14 +3280,14 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3303,14 +3311,14 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -3334,14 +3342,14 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -4860,10 +4868,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4878,7 +4886,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>33</v>
@@ -4899,7 +4907,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -4914,10 +4922,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4948,7 +4956,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -4964,16 +4972,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -4987,10 +4995,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
@@ -5044,10 +5052,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -5062,7 +5070,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>33</v>
@@ -5083,7 +5091,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -5098,10 +5106,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -5132,7 +5140,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -5148,16 +5156,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -5171,11 +5179,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -5228,10 +5236,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -5246,10 +5254,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -5267,7 +5275,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -5282,10 +5290,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -5316,7 +5324,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -5332,16 +5340,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -5355,10 +5363,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
@@ -5412,10 +5420,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -5430,10 +5438,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -5451,7 +5459,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -5466,10 +5474,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -5500,7 +5508,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -5516,16 +5524,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -5539,10 +5547,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="134">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -210,6 +210,18 @@
     <t xml:space="preserve">Talk prohibited room tag</t>
   </si>
   <si>
+    <t xml:space="preserve">Talk mutually-exclusive-talks tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk prerequisite talks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard penalty per talk that is scheduled before any of its prerequisite talks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Day</t>
   </si>
   <si>
@@ -334,6 +346,12 @@
   </si>
   <si>
     <t xml:space="preserve">Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutually exclusive talks tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prerequisite talks codes</t>
   </si>
   <si>
     <t xml:space="preserve">Pinned by user</t>
@@ -431,7 +449,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -459,6 +477,12 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -524,7 +548,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -546,6 +570,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -573,7 +601,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -597,7 +625,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -679,7 +707,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.7"/>
@@ -1037,6 +1065,30 @@
         <v>54</v>
       </c>
     </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1057,159 +1109,159 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="15"/>
+        <v>108</v>
+      </c>
+      <c r="C8" s="16"/>
       <c r="D8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>109</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1243,158 +1295,158 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>109</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1428,174 +1480,174 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="15"/>
+        <v>79</v>
+      </c>
+      <c r="B9" s="16"/>
       <c r="C9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>109</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1628,156 +1680,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1811,157 +1863,157 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="16"/>
+        <v>78</v>
+      </c>
+      <c r="B8" s="17"/>
       <c r="C8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1995,156 +2047,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>78</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2178,156 +2230,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>78</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2361,159 +2413,159 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>102</v>
+        <v>78</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>108</v>
       </c>
       <c r="C8" s="0"/>
-      <c r="D8" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2547,174 +2599,174 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>78</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>79</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2755,63 +2807,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -2864,37 +2916,37 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2903,10 +2955,10 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2915,10 +2967,10 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
@@ -2972,7 +3024,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2982,40 +3034,40 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -3023,7 +3075,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3042,7 +3094,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3061,7 +3113,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -3080,7 +3132,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3117,8 +3169,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W1048576"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Y65"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.95"/>
@@ -3138,94 +3190,102 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="19.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="0" width="6.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="6.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="24" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="19.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="6.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="6.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="26" style="0" width="8.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>101</v>
+        <v>62</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -3241,22 +3301,24 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="6"/>
+      <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
+      <c r="U2" s="7"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3272,22 +3334,24 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="6"/>
+      <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
+      <c r="U3" s="7"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3303,22 +3367,24 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="6"/>
+      <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
+      <c r="U4" s="7"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -3334,22 +3400,24 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="6"/>
+      <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
+      <c r="U5" s="7"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -3365,11 +3433,13 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="6"/>
+      <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
+      <c r="U6" s="7"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
@@ -3390,11 +3460,13 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="6"/>
+      <c r="S7" s="2"/>
       <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="U7" s="7"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -3415,11 +3487,13 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="6"/>
+      <c r="S9" s="2"/>
       <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
+      <c r="U9" s="7"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -3440,11 +3514,13 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="2"/>
       <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
+      <c r="U10" s="7"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -3465,11 +3541,13 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
-      <c r="S11" s="6"/>
+      <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
+      <c r="U11" s="7"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -3490,11 +3568,13 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="6"/>
+      <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
+      <c r="U12" s="7"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -3515,11 +3595,13 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="6"/>
+      <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="U13" s="7"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -3540,11 +3622,13 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="6"/>
+      <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
+      <c r="U14" s="7"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -3565,11 +3649,13 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="6"/>
+      <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
+      <c r="U15" s="7"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -3590,11 +3676,13 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="6"/>
+      <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
+      <c r="U16" s="7"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -3615,11 +3703,13 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="6"/>
+      <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
+      <c r="U17" s="7"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -3640,11 +3730,13 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="6"/>
+      <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
+      <c r="U18" s="7"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -3665,11 +3757,13 @@
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="6"/>
+      <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
+      <c r="U19" s="7"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -3690,11 +3784,13 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="6"/>
+      <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
+      <c r="U20" s="7"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -3715,11 +3811,13 @@
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="6"/>
+      <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
+      <c r="U21" s="7"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -3740,11 +3838,13 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="6"/>
+      <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
+      <c r="U22" s="7"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -3765,11 +3865,13 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="6"/>
+      <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
+      <c r="U23" s="7"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -3790,11 +3892,13 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
-      <c r="S24" s="6"/>
+      <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
+      <c r="U24" s="7"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -3815,11 +3919,13 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="6"/>
+      <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
+      <c r="U25" s="7"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -3840,11 +3946,13 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="6"/>
+      <c r="S26" s="2"/>
       <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
+      <c r="U26" s="7"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -3865,11 +3973,13 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="6"/>
+      <c r="S27" s="2"/>
       <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
+      <c r="U27" s="7"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -3890,11 +4000,13 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="6"/>
+      <c r="S28" s="2"/>
       <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
+      <c r="U28" s="7"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -3915,11 +4027,13 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="6"/>
+      <c r="S29" s="2"/>
       <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
+      <c r="U29" s="7"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -3940,11 +4054,13 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="6"/>
+      <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
+      <c r="U30" s="7"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -3965,11 +4081,13 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="6"/>
+      <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
+      <c r="U31" s="7"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -3990,11 +4108,13 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
-      <c r="S32" s="6"/>
+      <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
+      <c r="U32" s="7"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -4015,11 +4135,13 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="6"/>
+      <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
+      <c r="U33" s="7"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -4040,11 +4162,13 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="6"/>
+      <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
+      <c r="U34" s="7"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -4065,11 +4189,13 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="6"/>
+      <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
+      <c r="U35" s="7"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -4090,11 +4216,13 @@
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
-      <c r="S36" s="6"/>
+      <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
+      <c r="U36" s="7"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -4115,11 +4243,13 @@
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
-      <c r="S37" s="6"/>
+      <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
+      <c r="U37" s="7"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -4140,11 +4270,13 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
-      <c r="S38" s="6"/>
+      <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
+      <c r="U38" s="7"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -4165,11 +4297,13 @@
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="6"/>
+      <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
+      <c r="U39" s="7"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -4190,11 +4324,13 @@
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
-      <c r="S40" s="6"/>
+      <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
+      <c r="U40" s="7"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -4215,11 +4351,13 @@
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
-      <c r="S41" s="6"/>
+      <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
+      <c r="U41" s="7"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -4240,11 +4378,13 @@
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="6"/>
+      <c r="S42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
+      <c r="U42" s="7"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -4265,11 +4405,13 @@
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
-      <c r="S43" s="6"/>
+      <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
+      <c r="U43" s="7"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -4290,11 +4432,13 @@
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
-      <c r="S44" s="6"/>
+      <c r="S44" s="2"/>
       <c r="T44" s="2"/>
-      <c r="U44" s="2"/>
+      <c r="U44" s="7"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -4315,11 +4459,13 @@
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
-      <c r="S45" s="6"/>
+      <c r="S45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
+      <c r="U45" s="7"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -4340,11 +4486,13 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="6"/>
+      <c r="S46" s="2"/>
       <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
+      <c r="U46" s="7"/>
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -4365,11 +4513,13 @@
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
-      <c r="S47" s="6"/>
+      <c r="S47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
+      <c r="U47" s="7"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -4390,11 +4540,13 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
-      <c r="S48" s="6"/>
+      <c r="S48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
+      <c r="U48" s="7"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -4415,11 +4567,13 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="6"/>
+      <c r="S49" s="2"/>
       <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
+      <c r="U49" s="7"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
+      <c r="Y49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -4440,11 +4594,13 @@
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
-      <c r="S50" s="6"/>
+      <c r="S50" s="2"/>
       <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
+      <c r="U50" s="7"/>
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -4465,11 +4621,13 @@
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
-      <c r="S51" s="6"/>
+      <c r="S51" s="2"/>
       <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
+      <c r="U51" s="7"/>
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -4490,11 +4648,13 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
-      <c r="S52" s="6"/>
+      <c r="S52" s="2"/>
       <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
+      <c r="U52" s="7"/>
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -4515,11 +4675,13 @@
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
-      <c r="S53" s="6"/>
+      <c r="S53" s="2"/>
       <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
+      <c r="U53" s="7"/>
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -4540,11 +4702,13 @@
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
-      <c r="S54" s="6"/>
+      <c r="S54" s="2"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="2"/>
+      <c r="U54" s="7"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -4565,11 +4729,13 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
-      <c r="S55" s="6"/>
+      <c r="S55" s="2"/>
       <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
+      <c r="U55" s="7"/>
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -4590,11 +4756,13 @@
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
-      <c r="S56" s="6"/>
+      <c r="S56" s="2"/>
       <c r="T56" s="2"/>
-      <c r="U56" s="2"/>
+      <c r="U56" s="7"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -4615,11 +4783,13 @@
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
-      <c r="S57" s="6"/>
+      <c r="S57" s="2"/>
       <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
+      <c r="U57" s="7"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
+      <c r="X57" s="2"/>
+      <c r="Y57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -4640,11 +4810,13 @@
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
-      <c r="S58" s="6"/>
+      <c r="S58" s="2"/>
       <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
+      <c r="U58" s="7"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
+      <c r="Y58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -4665,11 +4837,13 @@
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
-      <c r="S59" s="6"/>
+      <c r="S59" s="2"/>
       <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
+      <c r="U59" s="7"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
+      <c r="X59" s="2"/>
+      <c r="Y59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -4690,11 +4864,13 @@
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="6"/>
+      <c r="S60" s="2"/>
       <c r="T60" s="2"/>
-      <c r="U60" s="2"/>
+      <c r="U60" s="7"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -4715,11 +4891,13 @@
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
-      <c r="S61" s="6"/>
+      <c r="S61" s="2"/>
       <c r="T61" s="2"/>
-      <c r="U61" s="2"/>
+      <c r="U61" s="7"/>
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
+      <c r="Y61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -4740,11 +4918,13 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
-      <c r="S62" s="6"/>
+      <c r="S62" s="2"/>
       <c r="T62" s="2"/>
-      <c r="U62" s="2"/>
+      <c r="U62" s="7"/>
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
+      <c r="Y62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -4765,11 +4945,13 @@
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="6"/>
+      <c r="S63" s="2"/>
       <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
+      <c r="U63" s="7"/>
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -4790,11 +4972,13 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="6"/>
+      <c r="S64" s="2"/>
       <c r="T64" s="2"/>
-      <c r="U64" s="2"/>
+      <c r="U64" s="7"/>
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
+      <c r="Y64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -4815,31 +4999,14 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="7"/>
+      <c r="S65" s="2"/>
       <c r="T65" s="2"/>
-      <c r="U65" s="2"/>
+      <c r="U65" s="8"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="X65" s="2"/>
+      <c r="Y65" s="2"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4860,157 +5027,157 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="16.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="16.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5051,17 +5218,17 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="17"/>
+      <c r="H1" s="18"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -5069,17 +5236,17 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="17"/>
+      <c r="H2" s="18"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -5087,17 +5254,17 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>116</v>
+      <c r="B3" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="17"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5106,16 +5273,16 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>117</v>
+        <v>120</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>123</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="17"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -5124,13 +5291,13 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="17"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="17"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -5140,32 +5307,32 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -5179,11 +5346,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -5228,157 +5395,157 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5412,156 +5579,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="A7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>76</v>
+      <c r="A8" s="17" t="s">
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,6 +26,11 @@
     <sheet name="Speaker unavailable timeslot 4" sheetId="16" state="visible" r:id="rId17"/>
     <sheet name="Speaker unavailable timeslot 5" sheetId="17" state="visible" r:id="rId18"/>
     <sheet name="Speaker conflict" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="Talk mutually-exclusive-talks tag" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="Talk mutually-exclusive-talks tag 2" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="Talk mutually-exclusive-talks tag 3" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="Talk mutually-exclusive-talks tag 4" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="Talk mutually-exclusive-talks tag 5" sheetId="23" state="visible" r:id="rId24"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="145">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -279,6 +284,9 @@
     <t xml:space="preserve">Normal room 2</t>
   </si>
   <si>
+    <t xml:space="preserve">Normal room 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unavailable room</t>
   </si>
   <si>
@@ -387,6 +395,18 @@
     <t xml:space="preserve">Talk with same speaker as normal talk</t>
   </si>
   <si>
+    <t xml:space="preserve">RedHat talk 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">redhat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RedHat talk 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RedHat talk 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Constraint package</t>
   </si>
   <si>
@@ -439,6 +459,24 @@
   </si>
   <si>
     <t xml:space="preserve">Speaker has conflicting timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutually exclusive talks in non-overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Mutually exclusive talks in overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutually exclusive talks in overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three Mutually exclusive talks in overlapping timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3hard/0soft</t>
   </si>
 </sst>
 </file>
@@ -479,16 +517,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -548,7 +585,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -570,10 +607,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -601,7 +634,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -625,8 +658,16 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1109,159 +1150,159 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="16"/>
+        <v>109</v>
+      </c>
+      <c r="C8" s="15"/>
       <c r="D8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1295,158 +1336,158 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1480,174 +1521,174 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="16"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1680,156 +1721,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1863,157 +1904,157 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2047,156 +2088,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="B8" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2230,156 +2271,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="B8" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2413,159 +2454,159 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>108</v>
+      <c r="B8" s="16" t="s">
+        <v>109</v>
       </c>
       <c r="C8" s="0"/>
-      <c r="D8" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="D8" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2599,175 +2640,360 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="B8" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-    </row>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2894,12 +3120,828 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
@@ -2965,7 +4007,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>80</v>
       </c>
@@ -2973,9 +4015,21 @@
         <v>69</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3037,28 +4091,28 @@
         <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>75</v>
@@ -3075,7 +4129,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3094,7 +4148,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3113,7 +4167,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -3132,7 +4186,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3201,70 +4255,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>62</v>
@@ -3273,19 +4327,19 @@
         <v>63</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -3303,7 +4357,7 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="7"/>
+      <c r="U2" s="6"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
@@ -3311,14 +4365,14 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3336,7 +4390,7 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="7"/>
+      <c r="U3" s="6"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
@@ -3344,14 +4398,14 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3369,7 +4423,7 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="7"/>
+      <c r="U4" s="6"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
@@ -3377,14 +4431,14 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -3402,7 +4456,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="7"/>
+      <c r="U5" s="6"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
@@ -3410,14 +4464,14 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -3435,16 +4489,20 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="7"/>
+      <c r="U6" s="6"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -3460,18 +4518,35 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="S7" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="T7" s="2"/>
-      <c r="U7" s="7"/>
+      <c r="U7" s="6"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
     </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -3487,9 +4562,11 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+      <c r="S9" s="0" t="s">
+        <v>118</v>
+      </c>
       <c r="T9" s="2"/>
-      <c r="U9" s="7"/>
+      <c r="U9" s="6"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
@@ -3516,7 +4593,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
-      <c r="U10" s="7"/>
+      <c r="U10" s="6"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
@@ -3543,7 +4620,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="7"/>
+      <c r="U11" s="6"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
@@ -3570,7 +4647,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="7"/>
+      <c r="U12" s="6"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
@@ -3597,7 +4674,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="7"/>
+      <c r="U13" s="6"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
@@ -3624,7 +4701,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="7"/>
+      <c r="U14" s="6"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
@@ -3651,7 +4728,7 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="7"/>
+      <c r="U15" s="6"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
@@ -3678,7 +4755,7 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="7"/>
+      <c r="U16" s="6"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
@@ -3705,7 +4782,7 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="7"/>
+      <c r="U17" s="6"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
@@ -3732,7 +4809,7 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="7"/>
+      <c r="U18" s="6"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
@@ -3759,7 +4836,7 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="7"/>
+      <c r="U19" s="6"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
@@ -3786,7 +4863,7 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="7"/>
+      <c r="U20" s="6"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
@@ -3813,7 +4890,7 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="7"/>
+      <c r="U21" s="6"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
@@ -3840,7 +4917,7 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="7"/>
+      <c r="U22" s="6"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
@@ -3867,7 +4944,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="7"/>
+      <c r="U23" s="6"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
@@ -3894,7 +4971,7 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="7"/>
+      <c r="U24" s="6"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
@@ -3921,7 +4998,7 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="7"/>
+      <c r="U25" s="6"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
@@ -3948,7 +5025,7 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
-      <c r="U26" s="7"/>
+      <c r="U26" s="6"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
@@ -3975,7 +5052,7 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
-      <c r="U27" s="7"/>
+      <c r="U27" s="6"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
@@ -4002,7 +5079,7 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
-      <c r="U28" s="7"/>
+      <c r="U28" s="6"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
@@ -4029,7 +5106,7 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
-      <c r="U29" s="7"/>
+      <c r="U29" s="6"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
@@ -4056,7 +5133,7 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="7"/>
+      <c r="U30" s="6"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
@@ -4083,7 +5160,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="7"/>
+      <c r="U31" s="6"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
@@ -4110,7 +5187,7 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="7"/>
+      <c r="U32" s="6"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
@@ -4137,7 +5214,7 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="7"/>
+      <c r="U33" s="6"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
@@ -4164,7 +5241,7 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="7"/>
+      <c r="U34" s="6"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
@@ -4191,7 +5268,7 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="7"/>
+      <c r="U35" s="6"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
@@ -4218,7 +5295,7 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="7"/>
+      <c r="U36" s="6"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
@@ -4245,7 +5322,7 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="7"/>
+      <c r="U37" s="6"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
@@ -4272,7 +5349,7 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="7"/>
+      <c r="U38" s="6"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
@@ -4299,7 +5376,7 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="7"/>
+      <c r="U39" s="6"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
@@ -4326,7 +5403,7 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="7"/>
+      <c r="U40" s="6"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
@@ -4353,7 +5430,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="7"/>
+      <c r="U41" s="6"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
@@ -4380,7 +5457,7 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="U42" s="7"/>
+      <c r="U42" s="6"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
@@ -4407,7 +5484,7 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="7"/>
+      <c r="U43" s="6"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
@@ -4434,7 +5511,7 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
-      <c r="U44" s="7"/>
+      <c r="U44" s="6"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
@@ -4461,7 +5538,7 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="7"/>
+      <c r="U45" s="6"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
@@ -4488,7 +5565,7 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
-      <c r="U46" s="7"/>
+      <c r="U46" s="6"/>
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
@@ -4515,7 +5592,7 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="U47" s="7"/>
+      <c r="U47" s="6"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
@@ -4542,7 +5619,7 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="U48" s="7"/>
+      <c r="U48" s="6"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
@@ -4569,7 +5646,7 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
-      <c r="U49" s="7"/>
+      <c r="U49" s="6"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
@@ -4596,7 +5673,7 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
-      <c r="U50" s="7"/>
+      <c r="U50" s="6"/>
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
@@ -4623,7 +5700,7 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
-      <c r="U51" s="7"/>
+      <c r="U51" s="6"/>
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
@@ -4650,7 +5727,7 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
-      <c r="U52" s="7"/>
+      <c r="U52" s="6"/>
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
@@ -4677,7 +5754,7 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
-      <c r="U53" s="7"/>
+      <c r="U53" s="6"/>
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
@@ -4704,7 +5781,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="7"/>
+      <c r="U54" s="6"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
@@ -4731,7 +5808,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
-      <c r="U55" s="7"/>
+      <c r="U55" s="6"/>
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
@@ -4758,7 +5835,7 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
-      <c r="U56" s="7"/>
+      <c r="U56" s="6"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
@@ -4785,7 +5862,7 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
-      <c r="U57" s="7"/>
+      <c r="U57" s="6"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
@@ -4812,7 +5889,7 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
-      <c r="U58" s="7"/>
+      <c r="U58" s="6"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
@@ -4839,7 +5916,7 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
-      <c r="U59" s="7"/>
+      <c r="U59" s="6"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
@@ -4866,7 +5943,7 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
-      <c r="U60" s="7"/>
+      <c r="U60" s="6"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
@@ -4893,7 +5970,7 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
-      <c r="U61" s="7"/>
+      <c r="U61" s="6"/>
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
       <c r="X61" s="2"/>
@@ -4920,7 +5997,7 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
-      <c r="U62" s="7"/>
+      <c r="U62" s="6"/>
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
       <c r="X62" s="2"/>
@@ -4947,7 +6024,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
-      <c r="U63" s="7"/>
+      <c r="U63" s="6"/>
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
@@ -4974,7 +6051,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
-      <c r="U64" s="7"/>
+      <c r="U64" s="6"/>
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
       <c r="X64" s="2"/>
@@ -5001,7 +6078,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
-      <c r="U65" s="8"/>
+      <c r="U65" s="7"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
       <c r="X65" s="2"/>
@@ -5027,157 +6104,157 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="16.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="16.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5218,17 +6295,17 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="18"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -5236,17 +6313,17 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="18"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -5254,17 +6331,17 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>122</v>
+      <c r="B3" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="18"/>
+      <c r="H3" s="17"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5273,16 +6350,16 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="18"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -5291,13 +6368,13 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="18"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -5311,19 +6388,19 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>75</v>
@@ -5350,7 +6427,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -5395,157 +6472,157 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5579,156 +6656,156 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="9" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="9" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="B4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>80</v>
+      <c r="A8" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="30"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,6 +31,14 @@
     <sheet name="Talk mutually-exclusive-talks tag 3" sheetId="21" state="visible" r:id="rId22"/>
     <sheet name="Talk mutually-exclusive-talks tag 4" sheetId="22" state="visible" r:id="rId23"/>
     <sheet name="Talk mutually-exclusive-talks tag 5" sheetId="23" state="visible" r:id="rId24"/>
+    <sheet name="Talk prerequisite talks" sheetId="24" state="visible" r:id="rId25"/>
+    <sheet name="Talk prerequisite talks 2" sheetId="25" state="visible" r:id="rId26"/>
+    <sheet name="Talk prerequisite talks 3" sheetId="26" state="visible" r:id="rId27"/>
+    <sheet name="Talk prerequisite talks 4" sheetId="27" state="visible" r:id="rId28"/>
+    <sheet name="Talk prerequisite talks 5" sheetId="28" state="visible" r:id="rId29"/>
+    <sheet name="Talk prerequisite talks 6" sheetId="29" state="visible" r:id="rId30"/>
+    <sheet name="Talk prerequisite talks 7" sheetId="30" state="visible" r:id="rId31"/>
+    <sheet name="Talk prerequisite talks 8" sheetId="31" state="visible" r:id="rId32"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -42,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="153">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -266,6 +274,9 @@
     <t xml:space="preserve">11:00</t>
   </si>
   <si>
+    <t xml:space="preserve">12:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
@@ -407,6 +418,43 @@
     <t xml:space="preserve">RedHat talk 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Talk with Normal talk as prerequisite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with Normal talk and Normal talk 2 as prerequisites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal talk, Normal talk2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Talk with (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Talk with Normal talk as prerequisite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) as a prerequisite</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Constraint package</t>
   </si>
   <si>
@@ -477,6 +525,15 @@
   </si>
   <si>
     <t xml:space="preserve">-3hard/0soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk scheduled after its prerequisites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:00-12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk scheduled before its prerequisites</t>
   </si>
 </sst>
 </file>
@@ -487,7 +544,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -515,6 +572,11 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -634,7 +696,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -658,11 +720,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1158,10 +1220,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1176,7 +1238,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>39</v>
@@ -1197,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1212,10 +1274,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1262,16 +1324,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1285,14 +1347,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1344,10 +1406,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1362,7 +1424,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>39</v>
@@ -1383,7 +1445,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1398,10 +1460,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1448,16 +1510,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1471,13 +1533,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1529,10 +1591,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1547,7 +1609,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>39</v>
@@ -1568,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1583,10 +1645,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1633,16 +1695,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1656,10 +1718,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1673,11 +1735,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -1729,10 +1791,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1747,7 +1809,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -1768,7 +1830,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1783,10 +1845,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1833,16 +1895,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1856,10 +1918,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -1912,10 +1974,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1930,7 +1992,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -1951,7 +2013,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1966,10 +2028,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2016,16 +2078,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2039,11 +2101,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2096,10 +2158,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2114,7 +2176,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2135,7 +2197,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2150,10 +2212,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2200,16 +2262,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2223,10 +2285,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2279,10 +2341,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2297,7 +2359,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2318,7 +2380,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2333,10 +2395,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2383,16 +2445,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2406,10 +2468,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2462,10 +2524,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2480,7 +2542,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2501,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2516,10 +2578,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2566,16 +2628,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2589,14 +2651,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -2648,10 +2710,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2666,7 +2728,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>43</v>
@@ -2687,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2702,10 +2764,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2752,16 +2814,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2775,10 +2837,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -2792,11 +2854,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -2848,10 +2910,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2866,7 +2928,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -2887,7 +2949,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2902,10 +2964,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2952,16 +3014,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2975,13 +3037,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -3093,7 +3155,20 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3137,10 +3212,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3155,7 +3230,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3176,7 +3251,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3191,10 +3266,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3241,16 +3316,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -3264,10 +3339,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="15"/>
@@ -3282,10 +3357,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -3338,10 +3413,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3356,7 +3431,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3377,7 +3452,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3392,10 +3467,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3442,16 +3517,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -3465,10 +3540,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -3484,11 +3559,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -3540,10 +3615,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3558,7 +3633,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3579,7 +3654,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3594,10 +3669,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3644,16 +3719,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -3667,14 +3742,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -3688,11 +3763,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -3744,10 +3819,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3762,7 +3837,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3783,7 +3858,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3798,10 +3873,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3848,16 +3923,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -3871,10 +3946,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -3890,11 +3965,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -3909,12 +3984,1162 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
+      <c r="B9" s="15"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="17.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="5" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:E6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3965,7 +5190,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>64</v>
@@ -3974,18 +5199,18 @@
         <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>69</v>
@@ -3997,7 +5222,7 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>69</v>
@@ -4009,7 +5234,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>69</v>
@@ -4021,7 +5246,7 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>69</v>
@@ -4034,6 +5259,378 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="8" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="8" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4088,40 +5685,40 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -4129,7 +5726,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4148,7 +5745,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4167,7 +5764,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -4186,7 +5783,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4255,70 +5852,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>62</v>
@@ -4327,19 +5924,19 @@
         <v>63</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -4365,14 +5962,14 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -4398,14 +5995,14 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -4431,14 +6028,14 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -4464,14 +6061,14 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -4497,7 +6094,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
@@ -4519,7 +6116,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="6"/>
@@ -4530,18 +6127,18 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
@@ -4563,7 +6160,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="6"/>
@@ -4572,10 +6169,14 @@
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -4592,17 +6193,23 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
+      <c r="T10" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="U10" s="6"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -4619,17 +6226,23 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
+      <c r="T11" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="U11" s="6"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -4646,7 +6259,9 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
+      <c r="T12" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="U12" s="6"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
@@ -6112,10 +7727,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -6130,7 +7745,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>33</v>
@@ -6151,7 +7766,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -6166,10 +7781,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -6216,16 +7831,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -6239,10 +7854,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
@@ -6296,10 +7911,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -6314,7 +7929,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>33</v>
@@ -6335,7 +7950,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -6350,10 +7965,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -6400,16 +8015,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -6423,11 +8038,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -6480,10 +8095,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -6498,7 +8113,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>37</v>
@@ -6519,7 +8134,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -6534,10 +8149,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -6584,16 +8199,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -6607,10 +8222,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
@@ -6664,10 +8279,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -6682,7 +8297,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>37</v>
@@ -6703,7 +8318,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -6718,10 +8333,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -6768,16 +8383,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -6791,10 +8406,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="30"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="153">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -289,6 +289,9 @@
     <t xml:space="preserve">10:00-11:00</t>
   </si>
   <si>
+    <t xml:space="preserve">11:00-12:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Normal room</t>
   </si>
   <si>
@@ -424,7 +427,7 @@
     <t xml:space="preserve">Talk with Normal talk and Normal talk 2 as prerequisites</t>
   </si>
   <si>
-    <t xml:space="preserve">Normal talk, Normal talk2</t>
+    <t xml:space="preserve">Normal talk, Normal talk 2</t>
   </si>
   <si>
     <r>
@@ -528,9 +531,6 @@
   </si>
   <si>
     <t xml:space="preserve">Talk scheduled after its prerequisites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:00-12:00</t>
   </si>
   <si>
     <t xml:space="preserve">Talk scheduled before its prerequisites</t>
@@ -1220,10 +1220,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>39</v>
@@ -1259,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1274,10 +1274,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -1347,14 +1347,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1406,10 +1406,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>39</v>
@@ -1445,7 +1445,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -1533,13 +1533,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1591,10 +1591,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>39</v>
@@ -1630,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1735,11 +1735,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -1791,10 +1791,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -1830,7 +1830,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1895,7 +1895,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -1974,10 +1974,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2013,7 +2013,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -2101,11 +2101,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2158,10 +2158,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2197,7 +2197,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2341,10 +2341,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2380,7 +2380,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
@@ -2524,10 +2524,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>41</v>
@@ -2563,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -2651,14 +2651,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -2710,10 +2710,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2728,7 +2728,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>43</v>
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -2854,11 +2854,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -2910,10 +2910,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -2949,7 +2949,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -3037,13 +3037,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -3212,10 +3212,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3251,7 +3251,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="15"/>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -3413,10 +3413,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3452,7 +3452,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3517,7 +3517,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -3559,11 +3559,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -3615,10 +3615,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3654,7 +3654,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -3742,14 +3742,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -3763,11 +3763,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -3819,10 +3819,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>57</v>
@@ -3858,7 +3858,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3873,10 +3873,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -3965,11 +3965,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="15"/>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4028,10 +4028,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -4067,7 +4067,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -4155,14 +4155,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -4176,7 +4176,7 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="20"/>
@@ -4230,10 +4230,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -4269,7 +4269,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -4357,14 +4357,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="16"/>
@@ -4436,10 +4436,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -4475,7 +4475,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4540,7 +4540,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -4552,7 +4552,7 @@
         <v>78</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -4565,17 +4565,17 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
@@ -4626,10 +4626,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -4810,10 +4810,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -4994,10 +4994,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -5166,15 +5166,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1014" min="7" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1014" min="8" style="0" width="8.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1015" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -5187,8 +5187,9 @@
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
@@ -5207,10 +5208,13 @@
       <c r="F2" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>69</v>
@@ -5222,7 +5226,7 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>69</v>
@@ -5234,7 +5238,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>69</v>
@@ -5246,7 +5250,7 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>69</v>
@@ -5258,7 +5262,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D1:G1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5287,10 +5291,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -5305,7 +5309,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -5341,10 +5345,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -5391,7 +5395,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -5414,14 +5418,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -5473,10 +5477,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -5491,7 +5495,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>59</v>
@@ -5527,10 +5531,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -5577,7 +5581,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -5600,14 +5604,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -5688,28 +5692,28 @@
         <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>76</v>
@@ -5720,13 +5724,15 @@
       <c r="L2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5745,7 +5751,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5764,7 +5770,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -5783,7 +5789,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -5801,9 +5807,8 @@
       <c r="O6" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:O1"/>
+  <mergeCells count="1">
+    <mergeCell ref="J1:M1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5852,70 +5857,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>62</v>
@@ -5924,19 +5929,19 @@
         <v>63</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -5962,14 +5967,14 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -5995,14 +6000,14 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -6028,14 +6033,14 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -6061,14 +6066,14 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -6094,7 +6099,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
@@ -6116,7 +6121,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="6"/>
@@ -6127,18 +6132,18 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
@@ -6160,7 +6165,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="6"/>
@@ -6171,7 +6176,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
@@ -6194,7 +6199,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U10" s="6"/>
       <c r="V10" s="2"/>
@@ -6204,7 +6209,7 @@
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
@@ -6227,7 +6232,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="U11" s="6"/>
       <c r="V11" s="2"/>
@@ -6237,7 +6242,7 @@
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
@@ -6260,7 +6265,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U12" s="6"/>
       <c r="V12" s="2"/>
@@ -7727,10 +7732,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -7745,7 +7750,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>33</v>
@@ -7766,7 +7771,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -7781,10 +7786,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -7831,7 +7836,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -7854,10 +7859,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
@@ -7911,10 +7916,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -7929,7 +7934,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>33</v>
@@ -7950,7 +7955,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -7965,10 +7970,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -8015,7 +8020,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -8038,11 +8043,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -8095,10 +8100,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -8113,7 +8118,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>37</v>
@@ -8134,7 +8139,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -8149,10 +8154,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -8199,7 +8204,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -8222,10 +8227,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
@@ -8279,10 +8284,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -8297,7 +8302,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>37</v>
@@ -8318,7 +8323,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -8333,10 +8338,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -8383,7 +8388,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>76</v>
@@ -8406,10 +8411,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="35"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -44,6 +44,11 @@
     <sheet name="Same day talks 3" sheetId="34" state="visible" r:id="rId35"/>
     <sheet name="Same day talks 4" sheetId="35" state="visible" r:id="rId36"/>
     <sheet name="Same day talks 5" sheetId="36" state="visible" r:id="rId37"/>
+    <sheet name="Popular talks 1" sheetId="37" state="visible" r:id="rId38"/>
+    <sheet name="Popular talks 2" sheetId="38" state="visible" r:id="rId39"/>
+    <sheet name="Popular talks 3" sheetId="39" state="visible" r:id="rId40"/>
+    <sheet name="Popular talks 4" sheetId="40" state="visible" r:id="rId41"/>
+    <sheet name="Popular talks 5" sheetId="41" state="visible" r:id="rId42"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -55,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="186">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -162,6 +167,12 @@
     <t xml:space="preserve">Soft penalty per common content/theme of 2 talks that are scheduled on different days</t>
   </si>
   <si>
+    <t xml:space="preserve">Popular talks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talk type of timeslot</t>
   </si>
   <si>
@@ -294,6 +305,9 @@
     <t xml:space="preserve">Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Capacity</t>
+  </si>
+  <si>
     <t xml:space="preserve">09:00-10:00</t>
   </si>
   <si>
@@ -318,6 +332,15 @@
     <t xml:space="preserve">Unavailable room</t>
   </si>
   <si>
+    <t xml:space="preserve">Room with capacity 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room with capacity 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room with capacity 200</t>
+  </si>
+  <si>
     <t xml:space="preserve">Required timeslot tags</t>
   </si>
   <si>
@@ -388,6 +411,12 @@
   </si>
   <si>
     <t xml:space="preserve">Prerequisite talks codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of likes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crowd control risk</t>
   </si>
   <si>
     <t xml:space="preserve">Pinned by user</t>
@@ -514,6 +543,15 @@
       </rPr>
       <t xml:space="preserve">) as a prerequisite</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with 5 likes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with 10 likes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with 20 likes</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint package</t>
@@ -678,6 +716,95 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">soft</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Talks with different popularity in same room</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">hard/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">soft</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Less popular talks in smaller rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One less popular talk in a bigger room than a more popular talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two less popular talk in a bigger room than a more popular talk</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">hard/-2soft</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Three less popular talk in a bigger room than a more popular talk</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">hard/-3soft</t>
     </r>
   </si>
 </sst>
@@ -1184,14 +1311,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1280,12 +1407,12 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>1</v>
@@ -1296,13 +1423,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1324,12 +1451,12 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>1</v>
@@ -1340,13 +1467,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1360,7 +1487,17 @@
         <v>62</v>
       </c>
     </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1390,10 +1527,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1408,10 +1545,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1429,7 +1566,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1444,10 +1581,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1478,7 +1615,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -1494,16 +1631,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1517,14 +1654,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -1576,10 +1713,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1594,10 +1731,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1615,7 +1752,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1630,10 +1767,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1664,7 +1801,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -1680,16 +1817,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1703,13 +1840,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -1761,10 +1898,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1779,10 +1916,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1800,7 +1937,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1815,10 +1952,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1849,7 +1986,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -1865,16 +2002,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1888,10 +2025,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -1905,11 +2042,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -1961,10 +2098,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1979,10 +2116,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2000,7 +2137,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2015,10 +2152,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2049,7 +2186,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2065,16 +2202,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2088,10 +2225,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2144,10 +2281,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2162,10 +2299,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2183,7 +2320,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2198,10 +2335,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2232,7 +2369,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2248,16 +2385,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2271,11 +2408,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2328,10 +2465,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2346,10 +2483,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2367,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2382,10 +2519,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2416,7 +2553,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2432,16 +2569,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2455,10 +2592,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2511,10 +2648,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2529,10 +2666,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2550,7 +2687,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2565,10 +2702,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2599,7 +2736,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2615,16 +2752,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2638,10 +2775,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2694,10 +2831,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2712,10 +2849,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2733,7 +2870,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2748,10 +2885,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2782,7 +2919,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2798,16 +2935,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2821,14 +2958,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="18" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -2880,10 +3017,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2898,10 +3035,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2919,7 +3056,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2934,10 +3071,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2968,7 +3105,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2984,16 +3121,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3007,10 +3144,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -3024,11 +3161,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -3080,10 +3217,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3098,10 +3235,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3119,7 +3256,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3134,10 +3271,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3168,7 +3305,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3184,16 +3321,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3207,13 +3344,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -3265,92 +3402,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3395,10 +3532,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3413,10 +3550,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3434,7 +3571,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3449,10 +3586,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3483,7 +3620,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3499,16 +3636,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3522,10 +3659,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
@@ -3540,10 +3677,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -3596,10 +3733,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3614,10 +3751,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3635,7 +3772,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3650,10 +3787,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3684,7 +3821,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3700,16 +3837,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3723,10 +3860,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -3742,11 +3879,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -3798,10 +3935,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3816,10 +3953,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3837,7 +3974,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3852,10 +3989,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3886,7 +4023,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3902,16 +4039,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3925,14 +4062,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="18" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -3946,11 +4083,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -4002,10 +4139,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4020,10 +4157,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4041,7 +4178,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4056,10 +4193,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4090,7 +4227,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4106,16 +4243,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4129,10 +4266,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -4148,11 +4285,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -4167,10 +4304,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4211,10 +4348,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4229,10 +4366,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4250,7 +4387,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4265,10 +4402,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4299,7 +4436,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4315,16 +4452,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4338,14 +4475,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="18" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -4359,7 +4496,7 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22"/>
@@ -4413,10 +4550,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4431,10 +4568,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4452,7 +4589,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4467,10 +4604,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4501,7 +4638,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4517,16 +4654,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4540,14 +4677,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -4561,10 +4698,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="18"/>
@@ -4619,10 +4756,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4637,10 +4774,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4658,7 +4795,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4673,10 +4810,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4707,7 +4844,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4723,19 +4860,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -4748,17 +4885,17 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -4809,10 +4946,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4827,10 +4964,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4848,7 +4985,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4863,10 +5000,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4897,7 +5034,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4913,16 +5050,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4936,10 +5073,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -4993,10 +5130,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5011,10 +5148,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5032,7 +5169,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5047,10 +5184,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5081,7 +5218,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5097,16 +5234,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5120,10 +5257,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -5177,10 +5314,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5195,10 +5332,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5216,7 +5353,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5231,10 +5368,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5265,7 +5402,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5281,16 +5418,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5304,10 +5441,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -5349,110 +5486,152 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1014" min="9" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1015" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1015" min="10" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1016" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="4"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="5" t="s">
-        <v>77</v>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="3"/>
+        <v>89</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="E1:H1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5481,10 +5660,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5499,10 +5678,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5520,7 +5699,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5535,10 +5714,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5569,7 +5748,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5585,16 +5764,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5608,14 +5787,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -5667,10 +5846,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5685,10 +5864,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5706,7 +5885,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5721,10 +5900,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5755,7 +5934,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5771,16 +5950,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5794,14 +5973,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -5853,10 +6032,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5871,7 +6050,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -5892,7 +6071,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5907,10 +6086,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5941,7 +6120,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5957,16 +6136,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5980,14 +6159,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -6039,10 +6218,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6057,7 +6236,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6078,7 +6257,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6093,10 +6272,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6127,12 +6306,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6145,19 +6324,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6170,15 +6349,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6229,10 +6408,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6247,7 +6426,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6268,7 +6447,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6283,10 +6462,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6317,12 +6496,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6335,19 +6514,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6360,15 +6539,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6419,10 +6598,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6437,7 +6616,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6458,7 +6637,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6473,10 +6652,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6507,12 +6686,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6525,19 +6704,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6550,15 +6729,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6609,10 +6788,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6627,7 +6806,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6648,7 +6827,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6663,10 +6842,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6697,12 +6876,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6715,19 +6894,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6740,15 +6919,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6761,6 +6940,616 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6817,64 +7606,64 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="O2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6893,7 +7682,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6912,7 +7701,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6931,7 +7720,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6951,6 +7740,424 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -6967,7 +8174,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y65"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.43"/>
@@ -6989,110 +8196,116 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="19.45"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="6.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="6.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="26" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="20" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="0" width="6.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="6.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="28" style="0" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>113</v>
+        <v>66</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="8" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -7105,31 +8318,33 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="9"/>
+      <c r="U2" s="2"/>
       <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+      <c r="W2" s="9"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="8" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -7142,22 +8357,24 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="9"/>
+      <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
+      <c r="W3" s="9"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -7175,22 +8392,24 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="9"/>
+      <c r="U4" s="2"/>
       <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
+      <c r="W4" s="9"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -7208,22 +8427,24 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="9"/>
+      <c r="U5" s="2"/>
       <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
+      <c r="W5" s="9"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -7241,29 +8462,31 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="9"/>
+      <c r="U6" s="2"/>
       <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
+      <c r="W6" s="9"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -7275,41 +8498,43 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="T7" s="2"/>
-      <c r="U7" s="9"/>
+      <c r="U7" s="2"/>
       <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
+      <c r="W7" s="9"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -7325,22 +8550,24 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="0" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="T9" s="2"/>
-      <c r="U9" s="9"/>
+      <c r="U9" s="2"/>
       <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
+      <c r="W9" s="9"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -7359,21 +8586,23 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="U10" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="U10" s="2"/>
       <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
+      <c r="W10" s="9"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -7392,21 +8621,23 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="U11" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="U11" s="2"/>
       <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
+      <c r="W11" s="9"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -7425,18 +8656,24 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="U12" s="9"/>
+        <v>138</v>
+      </c>
+      <c r="U12" s="2"/>
       <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
+      <c r="W12" s="9"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -7454,16 +8691,24 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="9"/>
+      <c r="U13" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
+      <c r="W13" s="9"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -7481,16 +8726,24 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="9"/>
+      <c r="U14" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
+      <c r="W14" s="9"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -7508,38 +8761,15 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="9"/>
+      <c r="U15" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
+      <c r="W15" s="9"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -7562,11 +8792,13 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="9"/>
+      <c r="U17" s="2"/>
       <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
+      <c r="W17" s="9"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -7589,11 +8821,13 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="9"/>
+      <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
+      <c r="W18" s="9"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -7616,11 +8850,13 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="9"/>
+      <c r="U19" s="2"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
+      <c r="W19" s="9"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -7643,11 +8879,13 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="9"/>
+      <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
+      <c r="W20" s="9"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -7670,11 +8908,13 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="9"/>
+      <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
+      <c r="W21" s="9"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -7697,11 +8937,13 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="9"/>
+      <c r="U22" s="2"/>
       <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
+      <c r="W22" s="9"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -7724,11 +8966,13 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="9"/>
+      <c r="U23" s="2"/>
       <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
+      <c r="W23" s="9"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -7751,11 +8995,13 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="9"/>
+      <c r="U24" s="2"/>
       <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
+      <c r="W24" s="9"/>
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -7778,11 +9024,13 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="9"/>
+      <c r="U25" s="2"/>
       <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
+      <c r="W25" s="9"/>
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -7805,11 +9053,13 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
-      <c r="U26" s="9"/>
+      <c r="U26" s="2"/>
       <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
+      <c r="W26" s="9"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -7832,11 +9082,13 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
-      <c r="U27" s="9"/>
+      <c r="U27" s="2"/>
       <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
+      <c r="W27" s="9"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -7859,11 +9111,13 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
-      <c r="U28" s="9"/>
+      <c r="U28" s="2"/>
       <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
+      <c r="W28" s="9"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -7886,11 +9140,13 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
-      <c r="U29" s="9"/>
+      <c r="U29" s="2"/>
       <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
+      <c r="W29" s="9"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -7913,11 +9169,13 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="9"/>
+      <c r="U30" s="2"/>
       <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
+      <c r="W30" s="9"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -7940,11 +9198,13 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="9"/>
+      <c r="U31" s="2"/>
       <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
+      <c r="W31" s="9"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -7967,11 +9227,13 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="9"/>
+      <c r="U32" s="2"/>
       <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
+      <c r="W32" s="9"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -7994,11 +9256,13 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="9"/>
+      <c r="U33" s="2"/>
       <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
+      <c r="W33" s="9"/>
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -8021,11 +9285,13 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="9"/>
+      <c r="U34" s="2"/>
       <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
+      <c r="W34" s="9"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -8048,11 +9314,13 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="9"/>
+      <c r="U35" s="2"/>
       <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
+      <c r="W35" s="9"/>
       <c r="X35" s="2"/>
       <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -8075,11 +9343,13 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="9"/>
+      <c r="U36" s="2"/>
       <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
+      <c r="W36" s="9"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -8102,11 +9372,13 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="9"/>
+      <c r="U37" s="2"/>
       <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
+      <c r="W37" s="9"/>
       <c r="X37" s="2"/>
       <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+      <c r="AA37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -8129,11 +9401,13 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="9"/>
+      <c r="U38" s="2"/>
       <c r="V38" s="2"/>
-      <c r="W38" s="2"/>
+      <c r="W38" s="9"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -8156,11 +9430,13 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="9"/>
+      <c r="U39" s="2"/>
       <c r="V39" s="2"/>
-      <c r="W39" s="2"/>
+      <c r="W39" s="9"/>
       <c r="X39" s="2"/>
       <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
+      <c r="AA39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -8183,11 +9459,13 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="9"/>
+      <c r="U40" s="2"/>
       <c r="V40" s="2"/>
-      <c r="W40" s="2"/>
+      <c r="W40" s="9"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
+      <c r="AA40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -8210,11 +9488,13 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="9"/>
+      <c r="U41" s="2"/>
       <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
+      <c r="W41" s="9"/>
       <c r="X41" s="2"/>
       <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -8237,11 +9517,13 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="U42" s="9"/>
+      <c r="U42" s="2"/>
       <c r="V42" s="2"/>
-      <c r="W42" s="2"/>
+      <c r="W42" s="9"/>
       <c r="X42" s="2"/>
       <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -8264,11 +9546,13 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="9"/>
+      <c r="U43" s="2"/>
       <c r="V43" s="2"/>
-      <c r="W43" s="2"/>
+      <c r="W43" s="9"/>
       <c r="X43" s="2"/>
       <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -8291,11 +9575,13 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
-      <c r="U44" s="9"/>
+      <c r="U44" s="2"/>
       <c r="V44" s="2"/>
-      <c r="W44" s="2"/>
+      <c r="W44" s="9"/>
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
+      <c r="Z44" s="2"/>
+      <c r="AA44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -8318,11 +9604,13 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="9"/>
+      <c r="U45" s="2"/>
       <c r="V45" s="2"/>
-      <c r="W45" s="2"/>
+      <c r="W45" s="9"/>
       <c r="X45" s="2"/>
       <c r="Y45" s="2"/>
+      <c r="Z45" s="2"/>
+      <c r="AA45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -8345,11 +9633,13 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
-      <c r="U46" s="9"/>
+      <c r="U46" s="2"/>
       <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
+      <c r="W46" s="9"/>
       <c r="X46" s="2"/>
       <c r="Y46" s="2"/>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -8372,11 +9662,13 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="U47" s="9"/>
+      <c r="U47" s="2"/>
       <c r="V47" s="2"/>
-      <c r="W47" s="2"/>
+      <c r="W47" s="9"/>
       <c r="X47" s="2"/>
       <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -8399,11 +9691,13 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="U48" s="9"/>
+      <c r="U48" s="2"/>
       <c r="V48" s="2"/>
-      <c r="W48" s="2"/>
+      <c r="W48" s="9"/>
       <c r="X48" s="2"/>
       <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -8426,11 +9720,13 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
-      <c r="U49" s="9"/>
+      <c r="U49" s="2"/>
       <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
+      <c r="W49" s="9"/>
       <c r="X49" s="2"/>
       <c r="Y49" s="2"/>
+      <c r="Z49" s="2"/>
+      <c r="AA49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -8453,11 +9749,13 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
-      <c r="U50" s="9"/>
+      <c r="U50" s="2"/>
       <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
+      <c r="W50" s="9"/>
       <c r="X50" s="2"/>
       <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -8480,11 +9778,13 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
-      <c r="U51" s="9"/>
+      <c r="U51" s="2"/>
       <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
+      <c r="W51" s="9"/>
       <c r="X51" s="2"/>
       <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
+      <c r="AA51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -8507,11 +9807,13 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
-      <c r="U52" s="9"/>
+      <c r="U52" s="2"/>
       <c r="V52" s="2"/>
-      <c r="W52" s="2"/>
+      <c r="W52" s="9"/>
       <c r="X52" s="2"/>
       <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
+      <c r="AA52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -8534,11 +9836,13 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
-      <c r="U53" s="9"/>
+      <c r="U53" s="2"/>
       <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
+      <c r="W53" s="9"/>
       <c r="X53" s="2"/>
       <c r="Y53" s="2"/>
+      <c r="Z53" s="2"/>
+      <c r="AA53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -8561,11 +9865,13 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="9"/>
+      <c r="U54" s="2"/>
       <c r="V54" s="2"/>
-      <c r="W54" s="2"/>
+      <c r="W54" s="9"/>
       <c r="X54" s="2"/>
       <c r="Y54" s="2"/>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -8588,11 +9894,13 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
-      <c r="U55" s="9"/>
+      <c r="U55" s="2"/>
       <c r="V55" s="2"/>
-      <c r="W55" s="2"/>
+      <c r="W55" s="9"/>
       <c r="X55" s="2"/>
       <c r="Y55" s="2"/>
+      <c r="Z55" s="2"/>
+      <c r="AA55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -8615,11 +9923,13 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
-      <c r="U56" s="9"/>
+      <c r="U56" s="2"/>
       <c r="V56" s="2"/>
-      <c r="W56" s="2"/>
+      <c r="W56" s="9"/>
       <c r="X56" s="2"/>
       <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
+      <c r="AA56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -8642,11 +9952,13 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
-      <c r="U57" s="9"/>
+      <c r="U57" s="2"/>
       <c r="V57" s="2"/>
-      <c r="W57" s="2"/>
+      <c r="W57" s="9"/>
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
+      <c r="Z57" s="2"/>
+      <c r="AA57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -8669,11 +9981,13 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
-      <c r="U58" s="9"/>
+      <c r="U58" s="2"/>
       <c r="V58" s="2"/>
-      <c r="W58" s="2"/>
+      <c r="W58" s="9"/>
       <c r="X58" s="2"/>
       <c r="Y58" s="2"/>
+      <c r="Z58" s="2"/>
+      <c r="AA58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -8696,11 +10010,13 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
-      <c r="U59" s="9"/>
+      <c r="U59" s="2"/>
       <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
+      <c r="W59" s="9"/>
       <c r="X59" s="2"/>
       <c r="Y59" s="2"/>
+      <c r="Z59" s="2"/>
+      <c r="AA59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -8723,11 +10039,13 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
-      <c r="U60" s="9"/>
+      <c r="U60" s="2"/>
       <c r="V60" s="2"/>
-      <c r="W60" s="2"/>
+      <c r="W60" s="9"/>
       <c r="X60" s="2"/>
       <c r="Y60" s="2"/>
+      <c r="Z60" s="2"/>
+      <c r="AA60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -8750,11 +10068,13 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
-      <c r="U61" s="9"/>
+      <c r="U61" s="2"/>
       <c r="V61" s="2"/>
-      <c r="W61" s="2"/>
+      <c r="W61" s="9"/>
       <c r="X61" s="2"/>
       <c r="Y61" s="2"/>
+      <c r="Z61" s="2"/>
+      <c r="AA61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -8777,11 +10097,13 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
-      <c r="U62" s="9"/>
+      <c r="U62" s="2"/>
       <c r="V62" s="2"/>
-      <c r="W62" s="2"/>
+      <c r="W62" s="9"/>
       <c r="X62" s="2"/>
       <c r="Y62" s="2"/>
+      <c r="Z62" s="2"/>
+      <c r="AA62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -8804,11 +10126,13 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
-      <c r="U63" s="9"/>
+      <c r="U63" s="2"/>
       <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
+      <c r="W63" s="9"/>
       <c r="X63" s="2"/>
       <c r="Y63" s="2"/>
+      <c r="Z63" s="2"/>
+      <c r="AA63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -8831,11 +10155,13 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
-      <c r="U64" s="9"/>
+      <c r="U64" s="2"/>
       <c r="V64" s="2"/>
-      <c r="W64" s="2"/>
+      <c r="W64" s="9"/>
       <c r="X64" s="2"/>
       <c r="Y64" s="2"/>
+      <c r="Z64" s="2"/>
+      <c r="AA64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -8858,11 +10184,13 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
-      <c r="U65" s="10"/>
+      <c r="U65" s="2"/>
       <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
+      <c r="W65" s="10"/>
       <c r="X65" s="2"/>
       <c r="Y65" s="2"/>
+      <c r="Z65" s="2"/>
+      <c r="AA65" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8892,10 +10220,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -8910,10 +10238,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -8931,7 +10259,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8946,10 +10274,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8980,7 +10308,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -8996,16 +10324,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -9019,10 +10347,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18"/>
@@ -9076,10 +10404,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -9094,10 +10422,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -9115,7 +10443,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -9130,10 +10458,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -9164,7 +10492,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -9180,16 +10508,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -9203,11 +10531,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -9260,10 +10588,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -9278,10 +10606,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -9299,7 +10627,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9314,10 +10642,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -9348,7 +10676,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -9364,16 +10692,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -9387,10 +10715,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18"/>
@@ -9444,10 +10772,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -9462,10 +10790,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -9483,7 +10811,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9498,10 +10826,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -9532,7 +10860,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -9548,16 +10876,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -9571,10 +10899,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="187">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">Soft reward per 2 talks that have the same timeslot and a different language</t>
   </si>
   <si>
-    <t xml:space="preserve">Speaker preferred timeslot tag</t>
+    <t xml:space="preserve">Speaker preferred timeslot tags</t>
   </si>
   <si>
     <t xml:space="preserve">Soft penalty per missing preferred tag in a talk's timeslot</t>
   </si>
   <si>
-    <t xml:space="preserve">Speaker undesired timeslot tag</t>
+    <t xml:space="preserve">Speaker undesired timeslot tags</t>
   </si>
   <si>
     <t xml:space="preserve">Soft penalty per undesired tag in a talk's timeslot</t>
   </si>
   <si>
-    <t xml:space="preserve">Talk preferred timeslot tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talk undesired timeslot tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speaker preferred room tag</t>
+    <t xml:space="preserve">Talk preferred timeslot tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk undesired timeslot tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speaker preferred room tags</t>
   </si>
   <si>
     <t xml:space="preserve">Soft penalty per missing preferred tag in a talk's room</t>
   </si>
   <si>
-    <t xml:space="preserve">Speaker undesired room tag</t>
+    <t xml:space="preserve">Speaker undesired room tags</t>
   </si>
   <si>
     <t xml:space="preserve">Soft penalty per undesired tag in a talk's room</t>
   </si>
   <si>
-    <t xml:space="preserve">Talk preferred room tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talk undesired room tag</t>
+    <t xml:space="preserve">Talk preferred room tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk undesired room tags</t>
   </si>
   <si>
     <t xml:space="preserve">Same day talks</t>
@@ -209,43 +209,43 @@
     <t xml:space="preserve">Hard penalty per pair of talks with the same speaker in overlapping timeslots</t>
   </si>
   <si>
-    <t xml:space="preserve">Speaker required timeslot tag</t>
+    <t xml:space="preserve">Speaker required timeslot tags</t>
   </si>
   <si>
     <t xml:space="preserve">Hard penalty per missing required tag in a talk's timeslot</t>
   </si>
   <si>
-    <t xml:space="preserve">Speaker prohibited timeslot tag</t>
+    <t xml:space="preserve">Speaker prohibited timeslot tags</t>
   </si>
   <si>
     <t xml:space="preserve">Hard penalty per prohibited tag in a talk's timeslot</t>
   </si>
   <si>
-    <t xml:space="preserve">Talk required timeslot tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talk prohibited timeslot tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speaker required room tag</t>
+    <t xml:space="preserve">Talk required timeslot tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speaker required room tags</t>
   </si>
   <si>
     <t xml:space="preserve">Hard penalty per missing required tag in a talk's room</t>
   </si>
   <si>
-    <t xml:space="preserve">Speaker prohibited room tag</t>
+    <t xml:space="preserve">Speaker prohibited room tags</t>
   </si>
   <si>
     <t xml:space="preserve">Hard penalty per prohibited tag in a talk's room</t>
   </si>
   <si>
-    <t xml:space="preserve">Talk required room tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talk prohibited room tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talk mutually-exclusive-talks tag</t>
+    <t xml:space="preserve">Talk required room tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk prohibited room tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk mutually-exclusive-talks tags</t>
   </si>
   <si>
     <t xml:space="preserve">Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
@@ -606,6 +606,9 @@
   </si>
   <si>
     <t xml:space="preserve">Speaker has conflicting timeslots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk mutually-exclusive-talks tag</t>
   </si>
   <si>
     <t xml:space="preserve">Mutually exclusive talks in non-overlapping timeslots</t>
@@ -3238,7 +3241,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3256,7 +3259,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3553,7 +3556,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3571,7 +3574,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3754,7 +3757,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3772,7 +3775,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3956,7 +3959,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3974,7 +3977,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3992,7 +3995,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4160,7 +4163,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4178,7 +4181,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4196,7 +4199,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4387,7 +4390,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4589,7 +4592,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4795,7 +4798,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4985,7 +4988,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5169,7 +5172,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5187,7 +5190,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5353,7 +5356,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5699,7 +5702,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5885,7 +5888,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6071,7 +6074,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6257,7 +6260,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6447,7 +6450,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6465,7 +6468,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6637,7 +6640,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6655,7 +6658,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6827,7 +6830,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6845,7 +6848,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7017,7 +7020,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7035,7 +7038,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7209,7 +7212,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7227,7 +7230,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7418,7 +7421,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7436,7 +7439,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7807,7 +7810,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7825,7 +7828,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8016,7 +8019,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8034,7 +8037,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="45"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -49,6 +49,11 @@
     <sheet name="Popular talks 3" sheetId="39" state="visible" r:id="rId40"/>
     <sheet name="Popular talks 4" sheetId="40" state="visible" r:id="rId41"/>
     <sheet name="Popular talks 5" sheetId="41" state="visible" r:id="rId42"/>
+    <sheet name="Crowd control" sheetId="42" state="visible" r:id="rId43"/>
+    <sheet name="Crowd control 2" sheetId="43" state="visible" r:id="rId44"/>
+    <sheet name="Crowd control 3" sheetId="44" state="visible" r:id="rId45"/>
+    <sheet name="Crowd control 4" sheetId="45" state="visible" r:id="rId46"/>
+    <sheet name="Crowd control 5" sheetId="46" state="visible" r:id="rId47"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -60,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="199">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -171,6 +176,12 @@
   </si>
   <si>
     <t xml:space="preserve">Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crowd control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
   </si>
   <si>
     <t xml:space="preserve">Talk type of timeslot</t>
@@ -552,6 +563,18 @@
   </si>
   <si>
     <t xml:space="preserve">Talk with 20 likes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with 1 crowd control risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with 2 crowd control risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk with 3 crowd control risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk2 with 3 crowd control risk</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint package</t>
@@ -809,6 +832,57 @@
       </rPr>
       <t xml:space="preserve">hard/-3soft</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Single normal talk and a pair of talks with greater than zero crowd control risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three talks with greater than zero crowd control risk</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">hard/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">soft</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Single talk with greater than zero crowd control risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three single talks with greater than zero crowd control risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two pair of talks with greater than zero crowd control risk</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1173,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C1048576"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.7"/>
@@ -1325,14 +1399,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1421,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
@@ -1437,13 +1511,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1465,12 +1539,12 @@
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
@@ -1481,13 +1555,13 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1501,7 +1575,17 @@
         <v>64</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1530,10 +1614,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1548,10 +1632,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1569,7 +1653,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1584,10 +1668,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1618,7 +1702,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -1634,16 +1718,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1657,14 +1741,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -1716,10 +1800,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1734,10 +1818,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1755,7 +1839,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1770,10 +1854,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1804,7 +1888,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -1820,16 +1904,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1843,13 +1927,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -1901,10 +1985,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1919,10 +2003,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1940,7 +2024,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1955,10 +2039,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1989,7 +2073,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2005,16 +2089,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2028,10 +2112,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -2045,11 +2129,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -2101,10 +2185,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2119,10 +2203,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2140,7 +2224,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2155,10 +2239,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2189,7 +2273,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2205,16 +2289,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2228,10 +2312,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2284,10 +2368,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2302,10 +2386,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2323,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2338,10 +2422,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2372,7 +2456,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2388,16 +2472,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2411,11 +2495,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2468,10 +2552,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2486,10 +2570,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2507,7 +2591,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2522,10 +2606,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2556,7 +2640,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2572,16 +2656,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2595,10 +2679,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2651,10 +2735,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2669,10 +2753,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2690,7 +2774,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2705,10 +2789,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2739,7 +2823,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2755,16 +2839,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2778,10 +2862,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
@@ -2834,10 +2918,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -2852,10 +2936,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2873,7 +2957,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2888,10 +2972,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2922,7 +3006,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2938,16 +3022,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2961,14 +3045,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -3020,10 +3104,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3038,10 +3122,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3059,7 +3143,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3074,10 +3158,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3108,7 +3192,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3124,16 +3208,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3147,10 +3231,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -3164,11 +3248,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -3220,10 +3304,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3238,10 +3322,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3259,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3274,10 +3358,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3308,7 +3392,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3324,16 +3408,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3347,13 +3431,13 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -3405,92 +3489,120 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>73</v>
+      <c r="D8" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3535,10 +3647,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3553,10 +3665,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3574,7 +3686,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3589,10 +3701,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3623,7 +3735,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3639,16 +3751,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3662,10 +3774,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
@@ -3680,10 +3792,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -3736,10 +3848,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3754,10 +3866,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3775,7 +3887,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3790,10 +3902,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -3824,7 +3936,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -3840,16 +3952,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3863,10 +3975,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -3882,11 +3994,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -3938,10 +4050,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3956,10 +4068,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3977,7 +4089,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3992,10 +4104,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4026,7 +4138,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4042,16 +4154,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4065,14 +4177,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -4086,11 +4198,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -4142,10 +4254,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4160,10 +4272,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4181,7 +4293,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4196,10 +4308,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4230,7 +4342,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4246,16 +4358,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4269,10 +4381,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -4288,11 +4400,11 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="17"/>
@@ -4307,10 +4419,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4351,10 +4463,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4369,10 +4481,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4390,7 +4502,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4405,10 +4517,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4439,7 +4551,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4455,16 +4567,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4478,14 +4590,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -4499,7 +4611,7 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="22"/>
@@ -4553,10 +4665,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4571,10 +4683,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4592,7 +4704,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4607,10 +4719,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4641,7 +4753,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4657,16 +4769,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4680,14 +4792,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -4701,10 +4813,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="18"/>
@@ -4759,10 +4871,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4777,10 +4889,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4798,7 +4910,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4813,10 +4925,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4847,7 +4959,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -4863,19 +4975,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -4888,17 +5000,17 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -4949,10 +5061,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4967,10 +5079,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4988,7 +5100,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5003,10 +5115,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5037,7 +5149,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5053,16 +5165,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5076,10 +5188,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -5133,10 +5245,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5151,10 +5263,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5172,7 +5284,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5187,10 +5299,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5221,7 +5333,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5237,16 +5349,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5260,10 +5372,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -5317,10 +5429,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5335,10 +5447,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5356,7 +5468,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5371,10 +5483,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5405,7 +5517,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5421,16 +5533,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5444,10 +5556,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -5489,7 +5601,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.91"/>
@@ -5498,8 +5610,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11.86"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1015" min="10" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.27"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1015" min="12" style="0" width="8.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1016" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -5509,51 +5622,59 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>82</v>
+      <c r="J2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -5562,11 +5683,11 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -5575,11 +5696,11 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -5588,11 +5709,11 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
@@ -5601,40 +5722,41 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>200</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5663,10 +5785,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5681,10 +5803,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5702,7 +5824,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5717,10 +5839,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5751,7 +5873,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5767,16 +5889,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5790,14 +5912,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -5849,10 +5971,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -5867,10 +5989,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -5888,7 +6010,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5903,10 +6025,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5937,7 +6059,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -5953,16 +6075,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -5976,14 +6098,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -6035,10 +6157,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6053,7 +6175,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6074,7 +6196,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6089,10 +6211,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6123,7 +6245,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -6139,16 +6261,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -6162,14 +6284,14 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
@@ -6221,10 +6343,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6239,7 +6361,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6260,7 +6382,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6275,10 +6397,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6309,12 +6431,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6327,19 +6449,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6352,15 +6474,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6411,10 +6533,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6429,7 +6551,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6450,7 +6572,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6465,10 +6587,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6499,12 +6621,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6517,19 +6639,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6542,15 +6664,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6601,10 +6723,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6619,7 +6741,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6640,7 +6762,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6655,10 +6777,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6689,12 +6811,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6707,19 +6829,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6732,15 +6854,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6791,10 +6913,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6809,7 +6931,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>33</v>
@@ -6830,7 +6952,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6845,10 +6967,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6879,12 +7001,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6897,19 +7019,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6922,15 +7044,15 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -6981,10 +7103,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -6999,7 +7121,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>35</v>
@@ -7020,7 +7142,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7035,10 +7157,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7069,12 +7191,12 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -7087,19 +7209,19 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -7112,17 +7234,17 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -7173,10 +7295,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -7191,7 +7313,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>35</v>
@@ -7212,7 +7334,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7227,10 +7349,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7261,7 +7383,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -7277,16 +7399,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -7300,10 +7422,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -7319,10 +7441,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="18"/>
@@ -7338,10 +7460,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7382,10 +7504,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -7400,7 +7522,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>35</v>
@@ -7421,7 +7543,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7436,10 +7558,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7470,7 +7592,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -7486,16 +7608,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -7509,10 +7631,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -7528,10 +7650,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="18"/>
@@ -7547,10 +7669,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7579,7 +7701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
@@ -7594,7 +7716,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="0" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1018" min="16" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1018" min="17" style="0" width="8.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1019" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -7609,64 +7732,70 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O1" s="4"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" s="1"/>
+      <c r="O2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -7685,7 +7814,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -7704,7 +7833,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -7723,7 +7852,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -7741,8 +7870,9 @@
       <c r="O6" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -7771,10 +7901,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -7789,7 +7919,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>35</v>
@@ -7810,7 +7940,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7825,10 +7955,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7859,7 +7989,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -7875,16 +8005,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -7898,10 +8028,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -7917,10 +8047,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="0"/>
@@ -7936,10 +8066,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7980,10 +8110,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -7998,7 +8128,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>35</v>
@@ -8019,7 +8149,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8034,10 +8164,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8068,7 +8198,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -8084,16 +8214,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -8107,10 +8237,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -8126,10 +8256,10 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="0"/>
@@ -8145,11 +8275,1081 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>142</v>
-      </c>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="0"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF00DCFF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8209,106 +9409,106 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -8322,7 +9522,9 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" s="9"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
@@ -8331,23 +9533,23 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -8361,7 +9563,9 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" s="9"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
@@ -8370,14 +9574,14 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -8396,7 +9600,9 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" s="9"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
@@ -8405,14 +9611,14 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -8431,7 +9637,9 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W5" s="9"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
@@ -8440,14 +9648,14 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -8466,7 +9674,9 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W6" s="9"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
@@ -8475,21 +9685,21 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -8501,11 +9711,13 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
+      <c r="V7" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W7" s="9"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
@@ -8514,30 +9726,33 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="V8" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -8553,11 +9768,13 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
+      <c r="V9" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="W9" s="9"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
@@ -8566,11 +9783,11 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -8589,7 +9806,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
@@ -8601,11 +9818,11 @@
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -8624,7 +9841,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
@@ -8636,11 +9853,11 @@
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -8659,7 +9876,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
@@ -8671,11 +9888,11 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -8706,11 +9923,11 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -8741,11 +9958,11 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -8774,10 +9991,25 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="V16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+      <c r="A17" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -8796,7 +10028,9 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
+      <c r="V17" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="W17" s="9"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
@@ -8804,9 +10038,13 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
+      <c r="A18" s="0" t="s">
+        <v>149</v>
+      </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -8825,7 +10063,9 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
+      <c r="V18" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="W18" s="9"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
@@ -8833,9 +10073,13 @@
       <c r="AA18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A19" s="0" t="s">
+        <v>150</v>
+      </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -8854,7 +10098,9 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
+      <c r="V19" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="W19" s="9"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
@@ -10223,10 +11469,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -10241,10 +11487,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -10262,7 +11508,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -10277,10 +11523,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -10311,7 +11557,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -10327,16 +11573,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -10350,10 +11596,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18"/>
@@ -10407,10 +11653,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -10425,10 +11671,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -10446,7 +11692,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -10461,10 +11707,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -10495,7 +11741,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -10511,16 +11757,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -10534,11 +11780,11 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
@@ -10591,10 +11837,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -10609,10 +11855,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -10630,7 +11876,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -10645,10 +11891,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -10679,7 +11925,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -10695,16 +11941,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -10718,10 +11964,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="18"/>
@@ -10775,10 +12021,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -10793,10 +12039,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -10814,7 +12060,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -10829,10 +12075,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -10863,7 +12109,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -10879,16 +12125,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -10902,10 +12148,10 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="45"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,11 +26,11 @@
     <sheet name="Speaker unavailable timeslot 4" sheetId="16" state="visible" r:id="rId17"/>
     <sheet name="Speaker unavailable timeslot 5" sheetId="17" state="visible" r:id="rId18"/>
     <sheet name="Speaker conflict" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="Talk mutually-exclusive-talks tag" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="Talk mutually-exclusive-talks tag 2" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="Talk mutually-exclusive-talks tags" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="Talk mutually-exclusive-talks tags 2" sheetId="20" state="visible" r:id="rId21"/>
     <sheet name="Talk mutually-exclusive-talks tag 3" sheetId="21" state="visible" r:id="rId22"/>
-    <sheet name="Talk mutually-exclusive-talks tag 4" sheetId="22" state="visible" r:id="rId23"/>
-    <sheet name="Talk mutually-exclusive-talks tag 5" sheetId="23" state="visible" r:id="rId24"/>
+    <sheet name="Talk mutually-exclusive-talks tags 4" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="Talk mutually-exclusive-talks tags 5" sheetId="23" state="visible" r:id="rId24"/>
     <sheet name="Talk prerequisite talks" sheetId="24" state="visible" r:id="rId25"/>
     <sheet name="Talk prerequisite talks 2" sheetId="25" state="visible" r:id="rId26"/>
     <sheet name="Talk prerequisite talks 3" sheetId="26" state="visible" r:id="rId27"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="200">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -632,6 +632,9 @@
   </si>
   <si>
     <t xml:space="preserve">Talk mutually-exclusive-talks tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
   </si>
   <si>
     <t xml:space="preserve">Mutually exclusive talks in non-overlapping timeslots</t>
@@ -3327,6 +3330,9 @@
       <c r="B2" s="21" t="s">
         <v>169</v>
       </c>
+      <c r="C2" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3343,7 +3349,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3670,6 +3676,9 @@
       <c r="B2" s="21" t="s">
         <v>169</v>
       </c>
+      <c r="C2" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3686,7 +3695,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3871,6 +3880,9 @@
       <c r="B2" s="21" t="s">
         <v>169</v>
       </c>
+      <c r="C2" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3887,7 +3899,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4073,6 +4085,9 @@
       <c r="B2" s="21" t="s">
         <v>169</v>
       </c>
+      <c r="C2" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -4089,7 +4104,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4107,7 +4122,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4277,6 +4292,9 @@
       <c r="B2" s="21" t="s">
         <v>169</v>
       </c>
+      <c r="C2" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -4293,7 +4311,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4311,7 +4329,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4502,7 +4520,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4704,7 +4722,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4910,7 +4928,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5100,7 +5118,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5284,7 +5302,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5302,7 +5320,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5468,7 +5486,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5824,7 +5842,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6010,7 +6028,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6196,7 +6214,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6382,7 +6400,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6572,7 +6590,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6590,7 +6608,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6762,7 +6780,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6780,7 +6798,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6952,7 +6970,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6970,7 +6988,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7142,7 +7160,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7160,7 +7178,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7334,7 +7352,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7352,7 +7370,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7543,7 +7561,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7561,7 +7579,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7940,7 +7958,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7958,7 +7976,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8149,7 +8167,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8167,7 +8185,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8358,7 +8376,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8376,7 +8394,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8572,7 +8590,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8590,7 +8608,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8786,7 +8804,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8804,7 +8822,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8996,7 +9014,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9014,7 +9032,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -9210,7 +9228,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9228,7 +9246,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -28,7 +28,7 @@
     <sheet name="Speaker conflict" sheetId="18" state="visible" r:id="rId19"/>
     <sheet name="Talk mutually-exclusive-talks tags" sheetId="19" state="visible" r:id="rId20"/>
     <sheet name="Talk mutually-exclusive-talks tags 2" sheetId="20" state="visible" r:id="rId21"/>
-    <sheet name="Talk mutually-exclusive-talks tag 3" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="Talk mutually-exclusive-talks tags 3" sheetId="21" state="visible" r:id="rId22"/>
     <sheet name="Talk mutually-exclusive-talks tags 4" sheetId="22" state="visible" r:id="rId23"/>
     <sheet name="Talk mutually-exclusive-talks tags 5" sheetId="23" state="visible" r:id="rId24"/>
     <sheet name="Talk prerequisite talks" sheetId="24" state="visible" r:id="rId25"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="198">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -629,12 +629,6 @@
   </si>
   <si>
     <t xml:space="preserve">Speaker has conflicting timeslots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talk mutually-exclusive-talks tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
   </si>
   <si>
     <t xml:space="preserve">Mutually exclusive talks in non-overlapping timeslots</t>
@@ -3328,10 +3322,7 @@
         <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3349,7 +3340,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3674,10 +3665,7 @@
         <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3695,7 +3683,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -3878,10 +3866,7 @@
         <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -3899,7 +3884,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4083,10 +4068,7 @@
         <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4104,7 +4086,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4122,7 +4104,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4290,10 +4272,7 @@
         <v>153</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4311,7 +4290,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4329,7 +4308,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -4520,7 +4499,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4722,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4928,7 +4907,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5118,7 +5097,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5302,7 +5281,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5320,7 +5299,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5486,7 +5465,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5842,7 +5821,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6028,7 +6007,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6214,7 +6193,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6400,7 +6379,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6590,7 +6569,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6608,7 +6587,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6780,7 +6759,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6798,7 +6777,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6970,7 +6949,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6988,7 +6967,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7160,7 +7139,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7178,7 +7157,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7352,7 +7331,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7370,7 +7349,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7561,7 +7540,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7579,7 +7558,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -7958,7 +7937,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -7976,7 +7955,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8167,7 +8146,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8185,7 +8164,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8376,7 +8355,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8394,7 +8373,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8590,7 +8569,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8608,7 +8587,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -8804,7 +8783,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -8822,7 +8801,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -9014,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9032,7 +9011,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -9228,7 +9207,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9246,7 +9225,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="23"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" state="visible" r:id="rId2"/>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Popular talks</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+    <t xml:space="preserve">Soft penalty per 2 talks where the less popular one (has lower favorite count) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
     <t xml:space="preserve">Crowd control</t>
@@ -424,7 +424,7 @@
     <t xml:space="preserve">Prerequisite talks codes</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of likes</t>
+    <t xml:space="preserve">Favorite count</t>
   </si>
   <si>
     <t xml:space="preserve">Crowd control risk</t>

--- a/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
+++ b/optaplanner-examples/src/test/resources/org/optaplanner/examples/conferencescheduling/solver/testConferenceSchedulingScoreRules.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="197">
   <si>
     <t xml:space="preserve">Conference name</t>
   </si>
@@ -184,6 +184,12 @@
     <t xml:space="preserve">Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
   </si>
   <si>
+    <t xml:space="preserve">Talk mutually-exclusive-talks tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talk type of timeslot</t>
   </si>
   <si>
@@ -256,12 +262,6 @@
     <t xml:space="preserve">Talk prohibited room tags</t>
   </si>
   <si>
-    <t xml:space="preserve">Talk mutually-exclusive-talks tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talk prerequisite talks</t>
   </si>
   <si>
@@ -442,42 +442,10 @@
     <t xml:space="preserve">Normal talk</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Normal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> theme tag</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Normal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> content tag</t>
-    </r>
+    <t xml:space="preserve">Normal theme tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal content tag</t>
   </si>
   <si>
     <t xml:space="preserve">Normal talk 2</t>
@@ -528,32 +496,7 @@
     <t xml:space="preserve">Normal talk, Normal talk 2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Talk with (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Talk with Normal talk as prerequisite</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) as a prerequisite</t>
-    </r>
+    <t xml:space="preserve">Talk with (Talk with Normal talk as prerequisite) as a prerequisite</t>
   </si>
   <si>
     <t xml:space="preserve">Talk with 5 likes</t>
@@ -592,13 +535,13 @@
     <t xml:space="preserve">Score</t>
   </si>
   <si>
-    <t xml:space="preserve">0hard/0soft</t>
+    <t xml:space="preserve">0hard/0medium/0soft</t>
   </si>
   <si>
     <t xml:space="preserve">Timeslot with non matching talk type</t>
   </si>
   <si>
-    <t xml:space="preserve">-1hard/0soft</t>
+    <t xml:space="preserve">-1hard/0medium/0soft</t>
   </si>
   <si>
     <t xml:space="preserve">Talk with available room</t>
@@ -634,19 +577,25 @@
     <t xml:space="preserve">Mutually exclusive talks in non-overlapping timeslots</t>
   </si>
   <si>
+    <t xml:space="preserve">0hard/0medium/-1soft</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not Mutually exclusive talks in overlapping timeslots</t>
   </si>
   <si>
     <t xml:space="preserve">Mutually exclusive talks in overlapping timeslots</t>
   </si>
   <si>
-    <t xml:space="preserve">-2hard/0soft</t>
+    <t xml:space="preserve">0hard/-1medium/-1soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0hard/-2medium/-3soft</t>
   </si>
   <si>
     <t xml:space="preserve">Three Mutually exclusive talks in overlapping timeslots</t>
   </si>
   <si>
-    <t xml:space="preserve">-3hard/0soft</t>
+    <t xml:space="preserve">0hard/-3medium/-3soft</t>
   </si>
   <si>
     <t xml:space="preserve">Talk scheduled after its prerequisites</t>
@@ -655,6 +604,9 @@
     <t xml:space="preserve">Talk scheduled before its prerequisites</t>
   </si>
   <si>
+    <t xml:space="preserve">-2hard/0medium/0soft</t>
+  </si>
+  <si>
     <t xml:space="preserve">Two talks with common theme and content tags on the same day</t>
   </si>
   <si>
@@ -664,123 +616,18 @@
     <t xml:space="preserve">Two talks with only same theme tags on different days</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hard/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soft</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Two talks with only same content tags on different days</t>
   </si>
   <si>
     <t xml:space="preserve">Two talks with same content and same theme tags on different days</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hard/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soft</t>
-    </r>
+    <t xml:space="preserve">0hard/0medium/-2soft</t>
   </si>
   <si>
     <t xml:space="preserve">Talks with different popularity in same room</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hard/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soft</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Less popular talks in smaller rooms</t>
   </si>
   <si>
@@ -790,87 +637,16 @@
     <t xml:space="preserve">Two less popular talk in a bigger room than a more popular talk</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hard/-2soft</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Three less popular talk in a bigger room than a more popular talk</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hard/-3soft</t>
-    </r>
+    <t xml:space="preserve">0hard/0medium/-3soft</t>
   </si>
   <si>
     <t xml:space="preserve">Single normal talk and a pair of talks with greater than zero crowd control risk</t>
   </si>
   <si>
     <t xml:space="preserve">Three talks with greater than zero crowd control risk</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hard/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soft</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Single talk with greater than zero crowd control risk</t>
@@ -890,7 +666,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -920,26 +696,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="4">
@@ -999,7 +759,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1020,7 +780,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1029,10 +789,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1056,16 +812,12 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1080,12 +832,8 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1170,7 +918,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.7"/>
@@ -1418,103 +1166,93 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1525,40 +1263,40 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1569,20 +1307,32 @@
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>66</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1603,24 +1353,24 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="10" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="10" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="13"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -1631,14 +1381,14 @@
       <c r="A2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>45</v>
+      <c r="B2" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="13"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -1649,14 +1399,14 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>161</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="13"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -1667,14 +1417,14 @@
       <c r="A4" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="13"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -1683,13 +1433,13 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
-      <c r="B5" s="13"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="13"/>
+      <c r="H5" s="12"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -1698,20 +1448,20 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
@@ -1743,19 +1493,19 @@
       <c r="B8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="15"/>
       <c r="D8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1789,24 +1539,24 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="10" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="10" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="13"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -1817,14 +1567,14 @@
       <c r="A2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>45</v>
+      <c r="B2" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="13"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -1835,14 +1585,14 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>162</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="13"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -1853,14 +1603,14 @@
       <c r="A4" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>158</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="13"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -1869,13 +1619,13 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
-      <c r="B5" s="13"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="13"/>
+      <c r="H5" s="12"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -1884,20 +1634,20 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
@@ -1932,15 +1682,15 @@
       <c r="C8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1974,24 +1724,24 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="11" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="11" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="10" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="27" style="10" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="13"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -2002,14 +1752,14 @@
       <c r="A2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>45</v>
+      <c r="B2" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="13"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -2020,14 +1770,14 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>163</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="13"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -2038,14 +1788,14 @@
       <c r="A4" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>156</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="13"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -2054,13 +1804,13 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
-      <c r="B5" s="13"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="13"/>
+      <c r="H5" s="12"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -2069,20 +1819,20 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
@@ -2114,34 +1864,34 @@
       <c r="B8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="17"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2174,24 +1924,24 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="26.13"/>
-    <co